--- a/Mudawwana_Deregistration_Bank_v1.1.0.xlsx
+++ b/Mudawwana_Deregistration_Bank_v1.1.0.xlsx
@@ -155,16 +155,16 @@
     <tableColumn id="1" name="#"/>
     <tableColumn id="2" name="ID"/>
     <tableColumn id="3" name="Service"/>
-    <tableColumn id="4" name="Section (EN)"/>
-    <tableColumn id="5" name="Section (AR)"/>
-    <tableColumn id="6" name="Subsection (EN)"/>
-    <tableColumn id="7" name="Subsection (AR)"/>
-    <tableColumn id="8" name="Type"/>
-    <tableColumn id="9" name="Comment (English)"/>
-    <tableColumn id="10" name="Comment (Arabic)"/>
-    <tableColumn id="11" name="Use only when (EN)"/>
-    <tableColumn id="12" name="Use only when (AR)"/>
-    <tableColumn id="13" name="Internal note"/>
+    <tableColumn id="4" name="Audience"/>
+    <tableColumn id="5" name="Type"/>
+    <tableColumn id="6" name="Section (EN)"/>
+    <tableColumn id="7" name="Section (AR)"/>
+    <tableColumn id="8" name="Subsection (EN)"/>
+    <tableColumn id="9" name="Subsection (AR)"/>
+    <tableColumn id="10" name="Comment (English)"/>
+    <tableColumn id="11" name="Comment (Arabic)"/>
+    <tableColumn id="12" name="Use only when (EN)"/>
+    <tableColumn id="13" name="Use only when (AR)"/>
     <tableColumn id="14" name="Search tags"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
@@ -172,22 +172,18 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Cases" displayName="Cases" ref="A1:M50" headerRowCount="1">
-  <autoFilter ref="A1:M50"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Cases" displayName="Cases" ref="A1:I50" headerRowCount="1">
+  <autoFilter ref="A1:I50"/>
+  <tableColumns count="9">
     <tableColumn id="1" name="#"/>
     <tableColumn id="2" name="Service"/>
     <tableColumn id="3" name="Case (EN)"/>
     <tableColumn id="4" name="Case (AR)"/>
-    <tableColumn id="5" name="Basis (EN)"/>
-    <tableColumn id="6" name="Basis (AR)"/>
-    <tableColumn id="7" name="Documents required (EN)"/>
-    <tableColumn id="8" name="Documents required (AR)"/>
-    <tableColumn id="9" name="Eligible date (EN)"/>
-    <tableColumn id="10" name="Eligible date (AR)"/>
-    <tableColumn id="11" name="Reviewer checks (EN)"/>
-    <tableColumn id="12" name="Reviewer checks (AR)"/>
-    <tableColumn id="13" name="Comments used"/>
+    <tableColumn id="5" name="Basis / outcome"/>
+    <tableColumn id="6" name="Documents required"/>
+    <tableColumn id="7" name="Eligible date"/>
+    <tableColumn id="8" name="Reviewer checks"/>
+    <tableColumn id="9" name="Comments used"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
@@ -488,20 +484,20 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="64" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
     <col width="64" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="64" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
     <col width="28" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -519,52 +515,52 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Audience</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Section (EN)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Section (AR)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Subsection (EN)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Subsection (AR)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Comment (English)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Comment (Arabic)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Use only when (EN)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Use only when (AR)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Internal note</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -589,46 +585,46 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>Common requirements</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>المتطلبات المشتركة</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Financial statement</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>البيان المالي</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Kindly attach a financial statement of the turnover (sales) and taxable expenses from the date of registration until today, on the company letterhead, signed by the authorised signatory and stamped. You may use the template available at: https://tax.gov.ae/ftatacsoft5cms/DataFolder/Files/Pdf/2022/Turnover%20Declaration%20Letter-REG-EN.docx</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>يرجى إرفاق بيان مالي بحجم الأعمال (المبيعات) والمصروفات الخاضعة للضريبة من تاريخ التسجيل حتى اليوم، على الورق الرسمي للشركة، موقعاً من المفوض بالتوقيع ومختوماً. يمكنكم استخدام النموذج المتاح على الرابط: https://tax.gov.ae/ftatacsoft5cms/DataFolder/Files/Pdf/2022/Turnover%20Declaration%20Letter-REG-EN.docx</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>The turnover can also be checked from Taxpayer Overview before asking.</t>
-        </is>
-      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>financial statement, turnover, sales, expenses, declaration, letterhead, template</t>
@@ -651,50 +647,54 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>Common requirements</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>المتطلبات المشتركة</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Sole establishment declaration</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>إقرار المؤسسات الفردية</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Kindly note that a natural person who owns several sole establishments is required to hold only one VAT registration covering all of them; separate registrations are not required. Therefore, kindly provide a letter declaring whether the owner, or any sole establishment owned by them, is registered for VAT, together with the relevant TRNs. If so, kindly confirm that you will file under one VAT-registered TRN. The letter must be signed and stamped (no stamp is required for a natural person). Kindly provide this declaration even if no such registrations exist.</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Kindly note that a natural person who owns several sole establishments is required to hold only one Value Added Tax (VAT) registration covering all of them; separate registrations are not required. Therefore, kindly provide a letter declaring whether the owner, or any sole establishment owned by them, is registered for VAT, together with the relevant TRNs. If so, kindly confirm that you will file under one VAT-registered Tax Registration Number (TRN). The letter must be signed and stamped (no stamp is required for a natural person). Kindly provide this declaration even if no such registrations exist.</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>يرجى العلم بأن الشخص الطبيعي الذي يملك عدة مؤسسات فردية يلزمه تسجيل واحد فقط لضريبة القيمة المضافة يشمل جميع مؤسساته، ولا يتطلب الأمر تسجيلات منفصلة. وعليه، يرجى تقديم خطاب يوضح ما إذا كان المالك أو أي مؤسسة فردية يملكها مسجلاً لضريبة القيمة المضافة مع ذكر أرقام التسجيل الضريبي. وفي حال وجودها، يرجى التأكيد على أنكم ستقدمون الإقرارات برقم تسجيل ضريبي واحد. ويجب أن يكون الخطاب موقعاً ومختوماً (لا يلزم الختم للشخص الطبيعي). يرجى تقديم هذا الإقرار حتى في حال عدم وجود تسجيلات أخرى.</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Only when the legal status of the entity is a sole establishment (check the owner from the Emirates ID number).</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>فقط عندما يكون الكيان مؤسسة فردية (تحقق من المالك عبر رقم الهوية الإماراتية).</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>sole establishment, natural person, declaration, one TRN, multiple establishments, owner</t>
@@ -717,42 +717,46 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>Common requirements</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>المتطلبات المشتركة</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Threshold declaration</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>إقرار حد التسجيل</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Kindly provide a declaration letter on the company letterhead confirming that you will not reach the mandatory registration threshold within the next month. The letter must be signed and stamped.</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم خطاب إقرار على الورق الرسمي للشركة يؤكد أنكم لن تتجاوزوا حد التسجيل الإلزامي خلال الشهر القادم، على أن يكون موقعاً ومختوماً.</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>declaration, threshold, mandatory, voluntary, next month, letterhead</t>
@@ -775,42 +779,46 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Notice</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>Common requirements</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>المتطلبات المشتركة</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Resubmission &amp; status notices</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>إشعارات إعادة التقديم والحالة</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Notice</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Kindly ensure that the resubmitted application includes all the documents and requirements listed above, to avoid further resubmissions of the application.</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>يرجى التأكد من أن الطلب المعاد تقديمه يتضمن جميع المستندات والمتطلبات المذكورة أعلاه، تفادياً لإعادة تقديم الطلب مرة أخرى.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>resubmit, all documents, complete, back and forth</t>
@@ -833,42 +841,46 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Notice</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>Common requirements</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>المتطلبات المشتركة</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Resubmission &amp; status notices</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>إشعارات إعادة التقديم والحالة</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Notice</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Your deregistration application has been pre-approved. Kindly submit the final VAT return, remove any draft applications and settle all outstanding liabilities so that the deregistration can be completed.</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Your deregistration application has been pre-approved. Kindly submit the final Value Added Tax (VAT) return, remove any draft applications and settle all outstanding liabilities so that the deregistration can be completed.</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>تمت الموافقة المبدئية على طلب إلغاء التسجيل. يرجى تقديم الإقرار الضريبي النهائي، وحذف أي طلبات في حالة مسودة، وسداد جميع الالتزامات المستحقة لاستكمال إلغاء التسجيل.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>pre-approved, final return, draft applications, liabilities, outstanding</t>
@@ -891,42 +903,46 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>Common requirements</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>المتطلبات المشتركة</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Resubmission &amp; status notices</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>إشعارات إعادة التقديم والحالة</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Request</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Kindly provide a clarification of the reason for applying for deregistration, together with any supporting documents.</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم توضيح لسبب التقدم بطلب إلغاء التسجيل، مع إرفاق أي مستندات داعمة.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>clarification, reason, deregistration, basis</t>
@@ -949,42 +965,46 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>Trade licence changes</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>تغييرات الرخصة التجارية</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Cancellation or liquidation</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>الإلغاء أو التصفية</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the official cancellation or liquidation certificate of the trade licence issued by the licensing authority. If the licence has not yet been cancelled or liquidated, kindly provide the board resolution and the last taxable invoice issued.</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم شهادة الإلغاء أو التصفية الرسمية للرخصة التجارية الصادرة عن جهة الترخيص. وفي حال لم يتم إلغاء الرخصة أو تصفيتها بعد، يرجى تقديم قرار مجلس الإدارة وآخر فاتورة ضريبية صادرة.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>cancellation, liquidation, certificate, licensing authority, board resolution, last invoice</t>
@@ -1007,42 +1027,46 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>Trade licence changes</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>تغييرات الرخصة التجارية</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Freezing of the licence</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>تجميد الرخصة</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the document or letter issued by the licensing authority confirming that the trade licence has been frozen.</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم المستند أو الخطاب الصادر عن جهة الترخيص الذي يثبت تجميد الرخصة التجارية.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>freeze, frozen licence, suspended, licensing authority</t>
@@ -1065,42 +1089,46 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>Trade licence changes</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>تغييرات الرخصة التجارية</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Change of legal status or owner</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>تغيير الشكل القانوني أو المالك</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Kindly provide the Memorandum of Association (MOA) or the contract evidencing the change in the legal status of the entity.</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Kindly provide the Memorandum of Association (Memorandum of Association) or the contract evidencing the change in the legal status of the entity.</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم عقد التأسيس أو العقد الذي يثبت تغيير الشكل القانوني للكيان.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>MOA, memorandum, contract, legal status, legal form, change</t>
@@ -1123,42 +1151,46 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>Trade licence changes</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>تغييرات الرخصة التجارية</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Change of legal status or owner</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>تغيير الشكل القانوني أو المالك</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Kindly provide the amended Memorandum of Association (MOA), or any official document evidencing the change in the legal status or ownership of the entity.</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Kindly provide the amended Memorandum of Association (Memorandum of Association), or any official document evidencing the change in the legal status or ownership of the entity.</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم عقد التأسيس المعدّل، أو أي مستند رسمي يثبت تغيير الشكل القانوني للكيان أو ملكيته.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>amended MOA, amendment, ownership, owner change, branch, legal status</t>
@@ -1181,42 +1213,46 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>Trade licence changes</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>تغييرات الرخصة التجارية</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Change of legal status or owner</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>تغيير الشكل القانوني أو المالك</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Kindly provide copies of both the previous and the current trade licence.</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم نسخة من الرخصة التجارية السابقة والرخصة التجارية الحالية.</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>old licence, new licence, trade license, before and after</t>
@@ -1239,50 +1275,54 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Rejection</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>Trade licence changes</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>تغييرات الرخصة التجارية</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Change of legal status or owner</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>تغيير الشكل القانوني أو المالك</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Rejection</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Please note that your deregistration application has been rejected, as the change in the legal status or ownership of the entity does not meet the conditions for VAT deregistration while the business continues to make taxable supplies above the voluntary registration threshold. Kindly apply for a VAT registration amendment to update your details instead.</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Please note that your deregistration application has been rejected, as the change in the legal status or ownership of the entity does not meet the conditions for Value Added Tax (VAT) deregistration while the business continues to make taxable supplies above the voluntary registration threshold. Kindly apply for a VAT registration amendment to update your details instead.</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>يرجى العلم بأنه تم رفض طلب إلغاء التسجيل، حيث إن تغيير الشكل القانوني للكيان أو ملكيته لا يستوفي شروط إلغاء التسجيل لضريبة القيمة المضافة ما دام النشاط مستمراً في تقديم توريدات خاضعة للضريبة تتجاوز حد التسجيل الاختياري. يرجى بدلاً من ذلك التقدم بطلب تعديل بيانات التسجيل لضريبة القيمة المضافة.</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>Turnover above the voluntary threshold after an LLC → LLC single owner / civil company change, or a change of owner.</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>حجم الأعمال أعلى من الحد الاختياري بعد تحويل ذ.م.م إلى ذ.م.م بمالك واحد / شركة مدنية، أو تغيير المالك.</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Turnover above the voluntary threshold after an limited liability company (LLC) → LLC single owner / civil company change, or a change of owner.</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>حجم الأعمال أعلى من الحد الاختياري بعد تحويل شركة ذات مسؤولية محدودة إلى شركة ذات مسؤولية محدودة بمالك واحد / شركة مدنية، أو تغيير المالك.</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>reject, amendment, above voluntary, LLC single owner, civil company, change owner, continue</t>
@@ -1305,42 +1345,46 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>Trade licence changes</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>تغييرات الرخصة التجارية</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Sale of sole establishment</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>بيع المؤسسة الفردية</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the sale contract of the sole establishment trade licence.</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم عقد بيع الرخصة التجارية للمؤسسة الفردية.</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>sale, selling contract, sold, sole establishment, transfer</t>
@@ -1363,50 +1407,54 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Rejection</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>Trade licence changes</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>تغييرات الرخصة التجارية</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Wrong registration</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>التسجيل الخاطئ</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Rejection</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Dear Taxpayer, please note that your deregistration application has been rejected, as the entity type recorded in your registration does not match the legal status shown in your trade licence. Kindly amend your legal entity type through the “Change Entity Type” application.</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>عزيزي الخاضع للضريبة، يرجى العلم بأنه تم رفض طلب إلغاء التسجيل، حيث إن نوع الكيان المسجل لا يتطابق مع الشكل القانوني الوارد في الرخصة التجارية. يرجى تعديل نوع الكيان القانوني من خلال طلب «تغيير نوع الكيان».</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Only after confirming from Taxpayer Overview that the entity type does not match the trade licence.</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>فقط بعد التأكد من ملخص الخاضع للضريبة أن نوع الكيان لا يطابق الرخصة التجارية.</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>wrong registration, entity type, change entity type, reject, mismatch</t>
@@ -1429,42 +1477,46 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>Trade licence changes</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>تغييرات الرخصة التجارية</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Cancellation or liquidation</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>الإلغاء أو التصفية</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Request</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the last taxable invoice issued by the entity.</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم آخر فاتورة ضريبية صادرة عن الكيان.</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>last invoice, taxable invoice, eligible date, last supply</t>
@@ -1487,42 +1539,46 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>Multiple TRNs &amp; branches</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>تعدد أرقام التسجيل والفروع</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Duplicate TRN / same owner</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>رقم تسجيل مكرر / المالك نفسه</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Request</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the Tax Registration Number (TRN) of the main company.</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>يرجى تزويدنا برقم التسجيل الضريبي للشركة الرئيسية.</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>main company, TRN, duplicate, parent</t>
@@ -1545,42 +1601,46 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>Multiple TRNs &amp; branches</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>تعدد أرقام التسجيل والفروع</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Duplicate TRN / same owner</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>رقم تسجيل مكرر / المالك نفسه</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Kindly provide a declaration letter on the company letterhead confirming that you will file your tax returns under the TRN of the main company. The letter must be signed and stamped.</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Kindly provide a declaration letter on the company letterhead confirming that you will file your tax returns under the Tax Registration Number (TRN) of the main company. The letter must be signed and stamped.</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم خطاب إقرار على الورق الرسمي للشركة يؤكد أنكم ستقدمون الإقرارات الضريبية برقم التسجيل الضريبي للشركة الرئيسية، على أن يكون موقعاً ومختوماً.</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>declaration, file with main, main TRN, letterhead, continue filing</t>
@@ -1603,42 +1663,46 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>Multiple TRNs &amp; branches</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>تعدد أرقام التسجيل والفروع</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Duplicate TRN / same owner</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>رقم تسجيل مكرر / المالك نفسه</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Request</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Kindly provide the Tax Registration Number (TRN) of the other entity registered for VAT under the same owner.</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Kindly provide the Tax Registration Number (TRN) of the other entity registered for Value Added Tax (VAT) under the same owner.</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>يرجى تزويدنا برقم التسجيل الضريبي للكيان الآخر المسجل لضريبة القيمة المضافة باسم المالك نفسه.</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>other entity, TRN, same owner, another sole establishment</t>
@@ -1661,42 +1725,46 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>Multiple TRNs &amp; branches</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>تعدد أرقام التسجيل والفروع</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>الفرع</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Request</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Kindly confirm whether the parent company holds a Tax Registration Number (TRN), and provide it if so.</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>يرجى تأكيد ما إذا كانت الشركة الأم تمتلك رقم تسجيل ضريبي، وتزويدنا به في حال وجوده.</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>branch, parent company, main TRN, confirm</t>
@@ -1719,42 +1787,46 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
           <t>Multiple TRNs &amp; branches</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>تعدد أرقام التسجيل والفروع</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>الفرع</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the trade licences of both the parent company and the branch.</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم الرخصة التجارية لكل من الشركة الأم والفرع.</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>branch, parent, trade licence, both licences</t>
@@ -1777,42 +1849,46 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>Multiple TRNs &amp; branches</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>تعدد أرقام التسجيل والفروع</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>الفرع</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the trade licence of the entity, showing that the registered establishment is a branch of it.</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم الرخصة التجارية للكيان بحيث يظهر فيها أن المنشأة المسجلة فرع تابع له.</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>branch, trade licence, mentioned, tax group member</t>
@@ -1835,42 +1911,46 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>Supplies &amp; thresholds</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>التوريدات وحدود التسجيل</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Zero-rated supplies</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>التوريدات الخاضعة لنسبة الصفر</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Kindly provide a signed and stamped declaration confirming that you will apply for an exception from VAT registration once the deregistration application is approved.</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Kindly provide a signed and stamped declaration confirming that you will apply for an exception from Value Added Tax (VAT) registration once the deregistration application is approved.</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم إقرار موقع ومختوم يؤكد أنكم ستتقدمون بطلب استثناء من التسجيل لضريبة القيمة المضافة فور الموافقة على طلب إلغاء التسجيل.</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>zero-rated, exception, declaration, exempt from registration</t>
@@ -1893,42 +1973,46 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>Supplies &amp; thresholds</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>التوريدات وحدود التسجيل</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Stopped making taxable supplies</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>التوقف عن التوريدات الخاضعة للضريبة</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Kindly provide a letter from the entity confirming that it has stopped making taxable supplies, stating the date on which the last taxable supply was made.</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم خطاب من الكيان يؤكد توقفه عن تقديم التوريدات الخاضعة للضريبة، مع بيان تاريخ آخر توريد خاضع للضريبة.</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="3" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>stopped, no longer, taxable supplies, online business, foreign company, letter</t>
@@ -1951,50 +2035,54 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Rejection</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>Supplies &amp; thresholds</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>التوريدات وحدود التسجيل</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>أقل من حد التسجيل</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Rejection</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Please note that your deregistration application has been rejected, as your taxable supplies over the last twelve months exceed the voluntary registration threshold and the business continues to make taxable supplies. Kindly apply for a VAT registration amendment if your registration details have changed.</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Please note that your deregistration application has been rejected, as your taxable supplies over the last twelve months exceed the voluntary registration threshold and the business continues to make taxable supplies. Kindly apply for a Value Added Tax (VAT) registration amendment if your registration details have changed.</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>يرجى العلم بأنه تم رفض طلب إلغاء التسجيل، حيث إن توريداتكم الخاضعة للضريبة خلال الاثني عشر شهراً الماضية تتجاوز حد التسجيل الاختياري وما زال النشاط مستمراً في تقديم توريدات خاضعة للضريبة. يرجى التقدم بطلب تعديل بيانات التسجيل في حال تغيّر بياناتكم.</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>Turnover above the voluntary threshold (AED 187,500) in the last 12 months.</t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="M25" s="3" t="inlineStr">
         <is>
           <t>حجم الأعمال أعلى من الحد الاختياري (187,500 درهم) خلال آخر 12 شهراً.</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>reject, above threshold, twelve months, continue, amendment</t>
@@ -2017,42 +2105,46 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Notice</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>Supplies &amp; thresholds</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>التوريدات وحدود التسجيل</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Below threshold</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>أقل من حد التسجيل</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Notice</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Kindly note that the deregistration will be processed on the basis that the business continues to make taxable supplies below the voluntary registration threshold. You remain obliged to monitor your taxable supplies and to register again if they exceed the registration threshold.</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>يرجى العلم بأن إلغاء التسجيل سيتم على أساس أن النشاط ما زال يقدم توريدات خاضعة للضريبة أقل من حد التسجيل الاختياري. وتظلون ملزمين بمتابعة توريداتكم الخاضعة للضريبة وإعادة التسجيل في حال تجاوزها حد التسجيل.</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="3" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>below voluntary, basis, monitor, register again, notice</t>
@@ -2075,42 +2167,46 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>Special cases</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>حالات خاصة</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Board members</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>أعضاء مجالس الإدارة</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the last invoice issued for the services performed as a member of a board of directors (director’s remuneration).</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم آخر فاتورة صادرة عن الخدمات المؤداة بصفة عضو في مجلس إدارة (مكافأة عضوية مجلس الإدارة).</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>board member, director, remuneration, reward, last invoice</t>
@@ -2133,42 +2229,46 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Notice</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>Special cases</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>حالات خاصة</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Board members</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>أعضاء مجالس الإدارة</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Notice</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Kindly note that, with effect from 1 January 2023, the functions of a member of a board of directors performed by a natural person are not considered a supply of services for VAT purposes, in accordance with the amended Article 3 of the Executive Regulation of the Federal Decree-Law on Value Added Tax.</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>يرجى العلم بأنه اعتباراً من 1 يناير 2023، لا تُعد مهام عضو مجلس الإدارة التي يؤديها شخص طبيعي توريداً للخدمات لأغراض ضريبة القيمة المضافة، وذلك وفقاً للمادة (3) المعدّلة من اللائحة التنفيذية للمرسوم بقانون اتحادي في شأن ضريبة القيمة المضافة.</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>board member, director, 2023, not a supply, public clarification, article 3</t>
@@ -2191,42 +2291,46 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Notice</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>Special cases</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>حالات خاصة</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Fund management</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>إدارة الصناديق</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Notice</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Kindly note that, with effect from 15 November 2024, the management of investment funds by a licensed fund manager is treated as an exempt supply in accordance with Cabinet Decision No. (100) of 2024 amending the Executive Regulation of the Federal Decree-Law on Value Added Tax.</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>يرجى العلم بأنه اعتباراً من 15 نوفمبر 2024، تُعامل إدارة صناديق الاستثمار من قبل مدير صندوق مرخص على أنها توريد معفى من الضريبة وفقاً لقرار مجلس الوزراء رقم (100) لسنة 2024 بتعديل اللائحة التنفيذية للمرسوم بقانون اتحادي في شأن ضريبة القيمة المضافة.</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>fund management, investment funds, exempt, 2024, cabinet decision 100</t>
@@ -2249,42 +2353,46 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>Special cases</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>حالات خاصة</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Passing of the owner</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>وفاة المالك</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the certificate of succession (inheritance limitation) issued by the competent court.</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم إعلام الوراثة (حصر الإرث) الصادر عن المحكمة المختصة.</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="3" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>death, passing, owner, inheritance, succession, court, heirs</t>
@@ -2307,42 +2415,46 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>Special cases</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>حالات خاصة</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Government entities</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>الجهات الحكومية</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the Cabinet Decision amending the list of Government Entities annexed to Cabinet Decision No. (58) of 2017, showing the removal of the entity from the list.</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم قرار مجلس الوزراء المعدِّل لقائمة الجهات الحكومية الملحقة بقرار مجلس الوزراء رقم (58) لسنة 2017، والذي يتضمن شطب الجهة من القائمة.</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>government entity, cabinet decision 58, list, removed</t>
@@ -2365,42 +2477,46 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>Special cases</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>حالات خاصة</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Charities</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>الجهات الخيرية</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the Cabinet Decision amending the list of Designated Charities annexed to Cabinet Decision No. (55) of 2017, showing the removal of the entity from the list.</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم قرار مجلس الوزراء المعدِّل لقائمة الجهات الخيرية المحددة الملحقة بقرار مجلس الوزراء رقم (55) لسنة 2017، والذي يتضمن شطب الجهة من القائمة.</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="3" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="3" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>charity, cabinet decision 55, list, removed, designated charities</t>
@@ -2423,42 +2539,46 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>Special cases</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>حالات خاصة</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Global Village</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>القرية العالمية</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the last contract signed between the entity and Global Village.</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم آخر عقد موقع بين الكيان والقرية العالمية.</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="3" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="3" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>global village, contract, season, last contract</t>
@@ -2481,42 +2601,46 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>Special cases</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>حالات خاصة</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Property owners</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>ملاك العقارات</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the building completion certificate issued by the competent authority.</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم شهادة إنجاز المبنى الصادرة عن الجهة المختصة.</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="3" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="3" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>property, completion certificate, building, residential, three years</t>
@@ -2539,42 +2663,46 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>Special cases</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>حالات خاصة</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Property owners</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>ملاك العقارات</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the sale contracts of all properties that have been sold.</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم عقود بيع جميع العقارات التي تم بيعها.</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>property, sale contract, sold, commercial, residential</t>
@@ -2597,50 +2725,54 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Rejection</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>Special cases</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>حالات خاصة</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Property owners</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>ملاك العقارات</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Rejection</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Please note that your deregistration application has been rejected. The sale of a commercial property that was not part of a continuing business activity does not constitute a basis for VAT registration; the registration is therefore considered to have been made in error. Kindly provide a clarification if you believe this assessment is incorrect.</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Please note that your deregistration application has been rejected. The sale of a commercial property that was not part of a continuing business activity does not constitute a basis for Value Added Tax (VAT) registration; the registration is therefore considered to have been made in error. Kindly provide a clarification if you believe this assessment is incorrect.</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
         <is>
           <t>يرجى العلم بأنه تم رفض طلب إلغاء التسجيل. إن بيع عقار تجاري لم يكن ضمن نشاط تجاري مستمر لا يُعد أساساً للتسجيل لضريبة القيمة المضافة، وبالتالي يُعتبر التسجيل قد تم عن طريق الخطأ. يرجى تقديم توضيح إذا كنتم ترون أن هذا التقييم غير صحيح.</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>Registered only to pay 5% on the sale of one or more commercial properties with no continuing business (basis: Others).</t>
         </is>
       </c>
-      <c r="L36" s="3" t="inlineStr">
+      <c r="M36" s="3" t="inlineStr">
         <is>
           <t>تم التسجيل فقط لسداد 5% على بيع عقار تجاري أو أكثر دون نشاط مستمر (الأساس: أخرى).</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>property, commercial, single property, wrong registration, business continuity, reject</t>
@@ -2663,42 +2795,46 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Notice</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>Special cases</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>حالات خاصة</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Former tax group members</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>الأعضاء السابقون في مجموعة ضريبية</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Notice</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Kindly note that the eligible date for deregistration cannot precede the date on which your TRN was activated following the deregistration or amendment of the tax group, as shown in the tax group application status log.</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Kindly note that the eligible date for deregistration cannot precede the date on which your Tax Registration Number (TRN) was activated following the deregistration or amendment of the tax group, as shown in the tax group application status log.</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>يرجى العلم بأن تاريخ الأهلية لإلغاء التسجيل لا يمكن أن يسبق تاريخ تفعيل رقم التسجيل الضريبي الخاص بكم بعد إلغاء تسجيل المجموعة الضريبية أو تعديلها، كما هو مبين في سجل حالة طلب المجموعة الضريبية.</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="3" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="3" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>tax group, member, activation date, eligible date, status log</t>
@@ -2721,42 +2857,46 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Notice</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>Special cases</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>حالات خاصة</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Owners’ associations</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr">
         <is>
           <t>جمعيات الملاك</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Notice</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>Kindly note that, following the transfer of all rights and obligations of Dubai Owners’ Associations to Management Entities on 3 November 2019, Dubai Owners’ Associations no longer make taxable supplies and were required to deregister no later than 4 December 2019.</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="K38" s="3" t="inlineStr">
         <is>
           <t>يرجى العلم بأنه عقب نقل جميع حقوق والتزامات جمعيات الملاك في دبي إلى جهات الإدارة بتاريخ 3 نوفمبر 2019، لم تعد جمعيات الملاك في دبي تقدم توريدات خاضعة للضريبة، وكان يتعين عليها إلغاء التسجيل في موعد أقصاه 4 ديسمبر 2019.</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="3" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="3" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>owners association, dubai, management entity, 2019, public clarification</t>
@@ -2779,42 +2919,46 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Licence, Liquidation &amp; Legal Changes</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>الرخصة والتصفية والتغييرات القانونية</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the official cancellation certificate of the trade licence issued by the licensing authority.</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="K39" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم شهادة الإلغاء الرسمية للرخصة التجارية الصادرة عن جهة الترخيص.</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>cancellation, trade licence, cessation, licensing authority</t>
@@ -2837,42 +2981,46 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Financial Statements &amp; Declarations</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>البيانات المالية والإقرارات</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the full financial statements for all the tax periods (balance sheet, trial balance and profit and loss statement), or a declaration letter of the revenues and assets, signed or stamped. Please note that the declaration letter must include the assets and revenues and must state the tax periods it covers.</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="K40" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم البيانات المالية الكاملة عن جميع الفترات الضريبية (الميزانية العمومية وميزان المراجعة وقائمة الأرباح والخسائر)، أو خطاب إقرار بالإيرادات والأصول موقعاً أو مختوماً. ويرجى ملاحظة أن خطاب الإقرار يجب أن يتضمن الأصول والإيرادات وأن يشير إلى الفترات الضريبية التي يغطيها.</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="3" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="3" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>financial statements, balance sheet, trial balance, profit and loss, declaration letter, revenue, assets, all tax periods</t>
@@ -2895,42 +3043,46 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Financial Statements &amp; Declarations</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>البيانات المالية والإقرارات</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the full financial statements for the relevant tax period (balance sheet, trial balance and profit and loss statement), signed and stamped.</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="K41" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم البيانات المالية الكاملة عن الفترة الضريبية المعنية (الميزانية العمومية وميزان المراجعة وقائمة الأرباح والخسائر)، موقعة ومختومة.</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="3" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="3" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>financial statements, relevant period, court liquidation, signed and stamped</t>
@@ -2953,42 +3105,46 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Offshore, Foreign &amp; Re-domiciliation</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
         <is>
           <t>الشركات الخارجية والأجنبية وإعادة التوطين</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the liquidation report, signed and stamped.</t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
+      <c r="K42" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم تقرير التصفية موقعاً ومختوماً.</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="3" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="3" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>liquidation report, offshore, signed and stamped</t>
@@ -3011,42 +3167,46 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Offshore, Foreign &amp; Re-domiciliation</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="I43" s="3" t="inlineStr">
         <is>
           <t>الشركات الخارجية والأجنبية وإعادة التوطين</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the board resolution, signed and stamped.</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم قرار مجلس الإدارة موقعاً ومختوماً.</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>board resolution, offshore, cessation date</t>
@@ -3069,42 +3229,46 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Offshore, Foreign &amp; Re-domiciliation</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="I44" s="3" t="inlineStr">
         <is>
           <t>الشركات الخارجية والأجنبية وإعادة التوطين</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>Kindly provide a declaration letter confirming that you do not have any of the following: a Permanent Establishment in the UAE under Article 14 of the Corporate Tax Decree-Law; State Sourced Income; a nexus in the UAE; or a person who habitually exercises an authority to conduct a business or business activity in the UAE on behalf of the foreign business.</t>
         </is>
       </c>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="K44" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم خطاب إقرار يؤكد عدم وجود أي مما يلي: منشأة دائمة في الدولة وفقاً للمادة (14) من المرسوم بقانون اتحادي في شأن ضريبة الشركات؛ أو دخل ناشئ في الدولة؛ أو صلة في الدولة؛ أو شخص يمارس بشكل معتاد صلاحية مزاولة أعمال أو نشاط أعمال في الدولة نيابةً عن الأعمال الأجنبية.</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>permanent establishment, article 14, state sourced income, nexus, foreign business, declaration, offshore, re-domiciliation</t>
@@ -3127,42 +3291,46 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Licence, Liquidation &amp; Legal Changes</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t>الرخصة والتصفية والتغييرات القانونية</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the liquidation decision issued by the court, clearly stating that the company has been dissolved and liquidated.</t>
         </is>
       </c>
-      <c r="J45" s="3" t="inlineStr">
+      <c r="K45" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم قرار التصفية الصادر عن المحكمة، على أن يُذكر فيه بوضوح أن الشركة قد تم حلّها وتصفيتها.</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>court, liquidation decision, dissolved, liquidated</t>
@@ -3185,42 +3353,46 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Notice</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Licence, Liquidation &amp; Legal Changes</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>الرخصة والتصفية والتغييرات القانونية</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Notice</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>Kindly ensure that the date of cessation stated in the application matches the date of the court decision.</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="K46" s="3" t="inlineStr">
         <is>
           <t>يرجى التأكد من تطابق تاريخ التوقف المذكور في الطلب مع تاريخ قرار المحكمة.</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="3" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="3" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>cessation date, court decision, match</t>
@@ -3243,42 +3415,46 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Licence, Liquidation &amp; Legal Changes</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="I47" s="3" t="inlineStr">
         <is>
           <t>الرخصة والتصفية والتغييرات القانونية</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the new trade licence.</t>
         </is>
       </c>
-      <c r="J47" s="3" t="inlineStr">
+      <c r="K47" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم الرخصة التجارية الجديدة.</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="3" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>new trade licence, sale, change of legal type</t>
@@ -3301,42 +3477,46 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Licence, Liquidation &amp; Legal Changes</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr">
         <is>
           <t>الرخصة والتصفية والتغييرات القانونية</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the sale agreement.</t>
         </is>
       </c>
-      <c r="J48" s="3" t="inlineStr">
+      <c r="K48" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم اتفاقية البيع.</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="3" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="3" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>sale agreement, sale of business</t>
@@ -3359,42 +3539,46 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Licence, Liquidation &amp; Legal Changes</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="I49" s="3" t="inlineStr">
         <is>
           <t>الرخصة والتصفية والتغييرات القانونية</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the merger agreement or contract.</t>
         </is>
       </c>
-      <c r="J49" s="3" t="inlineStr">
+      <c r="K49" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم اتفاقية أو عقد الاندماج.</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="3" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="3" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>merger, agreement, contract</t>
@@ -3417,42 +3601,46 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Offshore, Foreign &amp; Re-domiciliation</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="I50" s="3" t="inlineStr">
         <is>
           <t>الشركات الخارجية والأجنبية وإعادة التوطين</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the certificate of continuity.</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr">
+      <c r="K50" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم شهادة الاستمرارية.</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="3" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="3" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>certificate of continuity, re-domiciliation, continuance</t>
@@ -3475,50 +3663,54 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Offshore, Foreign &amp; Re-domiciliation</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>الشركات الخارجية والأجنبية وإعادة التوطين</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the trade licence deregistration (cancellation) document, as the entity is a foreign company holding a UAE trade licence.</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="K51" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم مستند إلغاء تسجيل الرخصة التجارية، حيث إن الكيان شركة أجنبية تحمل رخصة تجارية في الدولة.</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
+      <c r="L51" s="2" t="inlineStr">
         <is>
           <t>Only when the taxpayer is a foreign company holding a UAE trade licence.</t>
         </is>
       </c>
-      <c r="L51" s="3" t="inlineStr">
+      <c r="M51" s="3" t="inlineStr">
         <is>
           <t>فقط عندما يكون الخاضع للضريبة شركة أجنبية تحمل رخصة تجارية في الدولة.</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>foreign company, trade licence, deregistration, re-domiciliation</t>
@@ -3541,42 +3733,46 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Licence, Liquidation &amp; Legal Changes</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="I52" s="3" t="inlineStr">
         <is>
           <t>الرخصة والتصفية والتغييرات القانونية</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>Kindly provide evidence of the conversion of the legal type, according to the type of sole establishment.</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="K52" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم ما يثبت تحويل الشكل القانوني، بحسب نوع المؤسسة الفردية.</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="3" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="3" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>conversion, legal type, sole establishment, evidence</t>
@@ -3599,42 +3795,46 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Licence, Liquidation &amp; Legal Changes</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="I53" s="3" t="inlineStr">
         <is>
           <t>الرخصة والتصفية والتغييرات القانونية</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the Corporate Tax registration certificate issued for the new trade licence.</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr">
+      <c r="K53" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم شهادة التسجيل لضريبة الشركات الصادرة للرخصة التجارية الجديدة.</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="3" t="inlineStr"/>
-      <c r="M53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="3" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>CT certificate, new licence, new company, registration certificate</t>
@@ -3657,42 +3857,46 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Duplicate Registration</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>التسجيل المكرر</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Request</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>Kindly note that, in order to process the deregistration application, you are required to provide both the new and the old Corporate Tax registration certificates.</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
+      <c r="K54" s="3" t="inlineStr">
         <is>
           <t>يرجى العلم أنه لمعالجة طلب إلغاء التسجيل يتعين عليكم تقديم شهادتي التسجيل لضريبة الشركات الجديدة والقديمة.</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="3" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="3" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>duplicate registration, two certificates, old and new TRN</t>
@@ -3715,42 +3919,46 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Natural Person</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
         <is>
           <t>الشخص الطبيعي</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>Kindly provide the Memorandum of Association (where the sale or conversion was from a sole establishment to an LLC), or the sale agreement.</t>
-        </is>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Kindly provide the Memorandum of Association (where the sale or conversion was from a sole establishment to an limited liability company (LLC)), or the sale agreement.</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم عقد التأسيس (في حال تم البيع أو التحويل من مؤسسة فردية إلى شركة ذات مسؤولية محدودة)، أو اتفاقية البيع.</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="3" t="inlineStr"/>
-      <c r="M55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="3" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>MOA, sole to LLC, sale agreement, natural person</t>
@@ -3773,42 +3981,46 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Natural Person</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr">
         <is>
           <t>الشخص الطبيعي</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>Kindly provide a confirmation letter stating that you are not conducting any business, and are not registered with the FTA, under your name in the UAE.</t>
-        </is>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Kindly provide a confirmation letter stating that you are not conducting any business, and are not registered with the Federal Tax Authority (FTA), under your name in the UAE.</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم خطاب تأكيد بعدم مزاولتكم أي أعمال وعدم تسجيلكم لدى الهيئة الاتحادية للضرائب باسمكم في الدولة.</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="3" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="3" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>confirmation letter, no business, not registered, natural person, other TRN</t>
@@ -3831,42 +4043,46 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Natural Person</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t>الشخص الطبيعي</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the turnover declaration of the revenue for the relevant Gregorian calendar year, signed and stamped.</t>
         </is>
       </c>
-      <c r="J57" s="3" t="inlineStr">
+      <c r="K57" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم إقرار حجم الأعمال بالإيرادات عن السنة الميلادية المعنية، موقعاً ومختوماً.</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="3" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="3" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>turnover declaration, calendar year, natural person, revenue</t>
@@ -3889,42 +4105,46 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Natural Person</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="I58" s="3" t="inlineStr">
         <is>
           <t>الشخص الطبيعي</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the death certificate.</t>
         </is>
       </c>
-      <c r="J58" s="3" t="inlineStr">
+      <c r="K58" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم شهادة الوفاة.</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="3" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="3" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>death certificate, natural person, passing</t>
@@ -3947,42 +4167,46 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>Documents Requested</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>المستندات المطلوبة</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Natural Person</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr">
         <is>
           <t>الشخص الطبيعي</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>Kindly provide the full financial statements for 2024, 2025 and 2026 to date (balance sheet, trial balance and profit and loss statement), or a declaration letter of the revenues and assets, signed or stamped. Please note that the declaration letter must include the assets and revenues and must state the tax periods it covers.</t>
         </is>
       </c>
-      <c r="J59" s="3" t="inlineStr">
+      <c r="K59" s="3" t="inlineStr">
         <is>
           <t>يرجى تقديم البيانات المالية الكاملة عن السنوات 2024 و2025 و2026 حتى تاريخه (الميزانية العمومية وميزان المراجعة وقائمة الأرباح والخسائر)، أو خطاب إقرار بالإيرادات والأصول موقعاً أو مختوماً. ويرجى ملاحظة أن خطاب الإقرار يجب أن يتضمن الأصول والإيرادات وأن يشير إلى الفترات الضريبية التي يغطيها.</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="3" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="3" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>natural person, below 1 million, financial statements, 2024, 2025, 2026</t>
@@ -4005,42 +4229,46 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Rejection</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>Rejections</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>الرفض</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Rejection Sent to the Taxpayer</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr">
         <is>
           <t>رفض مُرسل إلى الخاضع للضريبة</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>Rejection</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>The deregistration application has been rejected due to incorrect registration details. You are not eligible for Corporate Tax deregistration; kindly amend your details through an Amend Taxable Person Details application or a Change Entity Type application.</t>
         </is>
       </c>
-      <c r="J60" s="3" t="inlineStr">
+      <c r="K60" s="3" t="inlineStr">
         <is>
           <t>تم رفض طلب إلغاء التسجيل بسبب عدم صحة بيانات التسجيل. أنتم غير مؤهلين لإلغاء التسجيل لضريبة الشركات؛ يرجى تعديل بياناتكم من خلال طلب تعديل بيانات الخاضع للضريبة أو طلب تغيير نوع الكيان.</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="3" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="3" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>reject, wrong registration, amend taxable person, change entity type</t>
@@ -4063,42 +4291,46 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Rejection</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>Rejections</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>الرفض</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Rejection Sent to the Taxpayer</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="I61" s="3" t="inlineStr">
         <is>
           <t>رفض مُرسل إلى الخاضع للضريبة</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Rejection</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="J61" s="2" t="inlineStr">
         <is>
           <t>The deregistration application has been rejected, as the business was sold without updating the legal type. Kindly apply for an Amend Taxable Person Details application to update the ownership details.</t>
         </is>
       </c>
-      <c r="J61" s="3" t="inlineStr">
+      <c r="K61" s="3" t="inlineStr">
         <is>
           <t>تم رفض طلب إلغاء التسجيل نظراً لبيع الأعمال دون تحديث الشكل القانوني. يرجى تقديم طلب تعديل بيانات الخاضع للضريبة لتحديث بيانات الملكية.</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="3" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="3" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>reject, sale of business, no change of legal type, ownership, AMTP</t>
@@ -4121,42 +4353,46 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Rejection</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
           <t>Rejections</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>الرفض</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Rejection Sent to the Taxpayer</t>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
+      <c r="I62" s="3" t="inlineStr">
         <is>
           <t>رفض مُرسل إلى الخاضع للضريبة</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>Rejection</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>The deregistration application cannot proceed, as the registration is linked with another tax type (VAT or Excise Tax). The duplicated TRN {{otherTrn}} must be deregistered.</t>
-        </is>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>The deregistration application cannot proceed, as the registration is linked with another tax type (VAT or Excise Tax). The duplicated Tax Registration Number (TRN) {{otherTrn}} must be deregistered.</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
         <is>
           <t>لا يمكن المضي في طلب إلغاء التسجيل نظراً لارتباط التسجيل بنوع ضريبة آخر (ضريبة القيمة المضافة أو الضريبة الانتقائية). يجب إلغاء تسجيل رقم التسجيل الضريبي المكرر {{otherTrn}}.</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="3" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>reject, duplicate, linked, VAT, excise, other TRN</t>
@@ -4179,42 +4415,46 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Rejection</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
           <t>Rejections</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>الرفض</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Rejection Sent to the Taxpayer</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="I63" s="3" t="inlineStr">
         <is>
           <t>رفض مُرسل إلى الخاضع للضريبة</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>Rejection</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>The deregistration application has been rejected due to repeated failure to submit the required documents. Kindly submit a new application once the requested documents are available.</t>
         </is>
       </c>
-      <c r="J63" s="3" t="inlineStr">
+      <c r="K63" s="3" t="inlineStr">
         <is>
           <t>تم رفض طلب إلغاء التسجيل بسبب التكرار في عدم تقديم المستندات المطلوبة. يرجى تقديم طلب جديد بعد توفر المستندات المطلوبة.</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="3" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="3" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>reject, documents not provided, repeated requests</t>
@@ -4237,42 +4477,46 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Rejection</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>Rejections</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>الرفض</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Rejection Sent to the Taxpayer</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr">
         <is>
           <t>رفض مُرسل إلى الخاضع للضريبة</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>Rejection</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="J64" s="2" t="inlineStr">
         <is>
           <t>The deregistration application has been rejected, as you are not eligible for deregistration: a Qualifying Public Benefit Entity must remain registered and submit the annual declaration, provided the conditions continue to be met.</t>
         </is>
       </c>
-      <c r="J64" s="3" t="inlineStr">
+      <c r="K64" s="3" t="inlineStr">
         <is>
           <t>تم رفض طلب إلغاء التسجيل نظراً لعدم أهليتكم لإلغاء التسجيل، إذ يتعين على جهة النفع العام المؤهلة البقاء مسجلة وتقديم الإقرار السنوي ما دامت الشروط مستوفاة.</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="3" t="inlineStr"/>
-      <c r="M64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>reject, QPBE, public benefit, cabinet decision 37, annual declaration</t>
@@ -4295,42 +4539,46 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Rejection</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>Rejections</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>الرفض</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Rejection Sent to the Taxpayer</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
+      <c r="I65" s="3" t="inlineStr">
         <is>
           <t>رفض مُرسل إلى الخاضع للضريبة</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>Rejection</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>The TRN deregistration cannot be processed because the trade licence is frozen. The trade licence must be cancelled in order to proceed with the deregistration.</t>
-        </is>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>The Tax Registration Number (TRN) deregistration cannot be processed because the trade licence is frozen. The trade licence must be cancelled in order to proceed with the deregistration.</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
         <is>
           <t>لا يمكن معالجة طلب إلغاء تسجيل رقم التسجيل الضريبي نظراً لأن الرخصة التجارية مجمّدة. يجب إلغاء الرخصة التجارية للمضي في إلغاء التسجيل.</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="3" t="inlineStr"/>
-      <c r="M65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>reject, frozen licence, freeze, cancel licence</t>
@@ -4353,42 +4601,46 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>To the taxpayer</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Rejection</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>Rejections</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>الرفض</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Rejection Sent to the Taxpayer</t>
         </is>
       </c>
-      <c r="G66" s="3" t="inlineStr">
+      <c r="I66" s="3" t="inlineStr">
         <is>
           <t>رفض مُرسل إلى الخاضع للضريبة</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Rejection</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>The deregistration application has been rejected, as the total reported revenue exceeds AED 1 million in the calendar year. Under the applicable guidelines, deregistration is not permitted in these circumstances.</t>
         </is>
       </c>
-      <c r="J66" s="3" t="inlineStr">
+      <c r="K66" s="3" t="inlineStr">
         <is>
           <t>تم رفض طلب إلغاء التسجيل نظراً لأن إجمالي الإيرادات المفصح عنها يتجاوز مليون درهم خلال السنة الميلادية. وبناءً على الإرشادات المعمول بها، لا يُسمح بإلغاء التسجيل في هذه الحالة.</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="3" t="inlineStr"/>
-      <c r="M66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="3" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>reject, natural person, above 1 million, threshold</t>
@@ -4411,42 +4663,58 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Juridical Person Cases</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr">
         <is>
           <t>حالات الشخص الاعتباري</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>Dear L2, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review: - The cessation date is as per the trade licence cancellation. - Declaration letter / financial statements have been provided covering all the tax periods up to the cessation date (signed or stamped). - The declaration letter / financial statements for the last period up to the cessation date show no fixed assets recorded. - No revenue was generated for the period {{period}} and the taxpayer elected for Small Business Relief (include all the periods of the CT returns). - There is no VAT or Excise Tax history on this TRN / the taxpayer has submitted a VAT deregistration application (to check). - Penalty imposed by {{penaltyBy}} / no penalty to be imposed (to check; if imposed manually and not through the system, mention it). All the above has been checked and the case is clear for L2 review and approval with no tax risk on this taxpayer.</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة: - تاريخ التوقف وفقاً لتاريخ إلغاء الرخصة التجارية. - تم تقديم خطاب إقرار / بيانات مالية تغطي جميع الفترات الضريبية حتى تاريخ التوقف (موقعة أو مختومة). - أظهر خطاب الإقرار / البيانات المالية عن الفترة الأخيرة حتى تاريخ التوقف عدم وجود أصول ثابتة مسجلة. - لم يتم تحقيق أي إيرادات خلال الفترة {{period}} وقد اختار الخاضع للضريبة إعفاء الأعمال الصغيرة (تُدرج جميع فترات إقرارات ضريبة الشركات). - لا يوجد سجل لضريبة القيمة المضافة أو الضريبة الانتقائية على رقم التسجيل هذا / قدّم الخاضع للضريبة طلب إلغاء التسجيل لضريبة القيمة المضافة (للتحقق). - تم فرض غرامة بواسطة {{penaltyBy}} / لا توجد غرامة مستحقة (للتحقق؛ في حال فرضها يدوياً وليس عبر النظام تجب الإشارة إلى ذلك). تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="3" t="inlineStr"/>
-      <c r="M67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Dear Level 2 reviewer, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review:
+- The cessation date is as per the trade licence cancellation.
+- Declaration letter / financial statements have been provided covering all the tax periods up to the cessation date (signed or stamped).
+- The declaration letter / financial statements for the last period up to the cessation date show no fixed assets recorded.
+- No revenue was generated for the period {{period}} and the taxpayer elected for Small Business Relief (include all the periods of the Corporate Tax returns).
+- There is no Value Added Tax (VAT) or Excise Tax history on this Tax Registration Number (TRN) / the taxpayer has submitted a VAT deregistration application (to check).
+- Penalty imposed by {{penaltyBy}} / no penalty to be imposed (to check; if imposed manually and not through the system, mention it). All the above has been checked and the case is clear for Level 2 review and approval with no tax risk on this taxpayer.</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة:
+- تاريخ التوقف وفقاً لتاريخ إلغاء الرخصة التجارية.
+- تم تقديم خطاب إقرار / بيانات مالية تغطي جميع الفترات الضريبية حتى تاريخ التوقف (موقعة أو مختومة).
+- أظهر خطاب الإقرار / البيانات المالية عن الفترة الأخيرة حتى تاريخ التوقف عدم وجود أصول ثابتة مسجلة.
+- لم يتم تحقيق أي إيرادات خلال الفترة {{period}} وقد اختار الخاضع للضريبة إعفاء الأعمال الصغيرة (تُدرج جميع فترات إقرارات ضريبة الشركات).
+- لا يوجد سجل لضريبة القيمة المضافة أو الضريبة الانتقائية على رقم التسجيل هذا / قدّم الخاضع للضريبة طلب إلغاء التسجيل لضريبة القيمة المضافة (للتحقق).
+- تم فرض غرامة بواسطة {{penaltyBy}} / لا توجد غرامة مستحقة (للتحقق؛ في حال فرضها يدوياً وليس عبر النظام تجب الإشارة إلى ذلك). تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="3" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>internal, L1, L2, cessation, no revenue, SBR</t>
@@ -4469,42 +4737,58 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="G68" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Juridical Person Cases</t>
         </is>
       </c>
-      <c r="G68" s="3" t="inlineStr">
+      <c r="I68" s="3" t="inlineStr">
         <is>
           <t>حالات الشخص الاعتباري</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>Dear L2, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review: - The cessation date is as per the trade licence cancellation. - Declaration letter / financial statements have been provided covering all the tax periods up to the cessation date (signed or stamped). - The declaration letter / financial statements for the last period up to the cessation date show no fixed assets recorded. - The total revenue is below AED 3 million for the tax period {{period}} and the taxpayer elected for Small Business Relief (include all the tax periods of the CT returns). - There is no VAT or Excise Tax history on this TRN / the taxpayer has submitted a VAT deregistration application (to check). - Penalty imposed by {{penaltyBy}} / no penalty to be imposed (to check; if imposed manually and not through the system, mention it). All the above has been checked and the case is clear for L2 review and approval with no tax risk on this taxpayer.</t>
-        </is>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة: - تاريخ التوقف وفقاً لتاريخ إلغاء الرخصة التجارية. - تم تقديم خطاب إقرار / بيانات مالية تغطي جميع الفترات الضريبية حتى تاريخ التوقف (موقعة أو مختومة). - أظهر خطاب الإقرار / البيانات المالية عن الفترة الأخيرة حتى تاريخ التوقف عدم وجود أصول ثابتة مسجلة. - إجمالي الإيرادات أقل من 3 ملايين درهم عن الفترة الضريبية {{period}} وقد اختار الخاضع للضريبة إعفاء الأعمال الصغيرة (تُدرج جميع الفترات الضريبية لإقرارات ضريبة الشركات). - لا يوجد سجل لضريبة القيمة المضافة أو الضريبة الانتقائية على رقم التسجيل هذا / قدّم الخاضع للضريبة طلب إلغاء التسجيل لضريبة القيمة المضافة (للتحقق). - تم فرض غرامة بواسطة {{penaltyBy}} / لا توجد غرامة مستحقة (للتحقق؛ في حال فرضها يدوياً وليس عبر النظام تجب الإشارة إلى ذلك). تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="3" t="inlineStr"/>
-      <c r="M68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Dear Level 2 reviewer, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review:
+- The cessation date is as per the trade licence cancellation.
+- Declaration letter / financial statements have been provided covering all the tax periods up to the cessation date (signed or stamped).
+- The declaration letter / financial statements for the last period up to the cessation date show no fixed assets recorded.
+- The total revenue is below AED 3 million for the tax period {{period}} and the taxpayer elected for Small Business Relief (include all the tax periods of the Corporate Tax returns).
+- There is no Value Added Tax (VAT) or Excise Tax history on this Tax Registration Number (TRN) / the taxpayer has submitted a VAT deregistration application (to check).
+- Penalty imposed by {{penaltyBy}} / no penalty to be imposed (to check; if imposed manually and not through the system, mention it). All the above has been checked and the case is clear for Level 2 review and approval with no tax risk on this taxpayer.</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة:
+- تاريخ التوقف وفقاً لتاريخ إلغاء الرخصة التجارية.
+- تم تقديم خطاب إقرار / بيانات مالية تغطي جميع الفترات الضريبية حتى تاريخ التوقف (موقعة أو مختومة).
+- أظهر خطاب الإقرار / البيانات المالية عن الفترة الأخيرة حتى تاريخ التوقف عدم وجود أصول ثابتة مسجلة.
+- إجمالي الإيرادات أقل من 3 ملايين درهم عن الفترة الضريبية {{period}} وقد اختار الخاضع للضريبة إعفاء الأعمال الصغيرة (تُدرج جميع الفترات الضريبية لإقرارات ضريبة الشركات).
+- لا يوجد سجل لضريبة القيمة المضافة أو الضريبة الانتقائية على رقم التسجيل هذا / قدّم الخاضع للضريبة طلب إلغاء التسجيل لضريبة القيمة المضافة (للتحقق).
+- تم فرض غرامة بواسطة {{penaltyBy}} / لا توجد غرامة مستحقة (للتحقق؛ في حال فرضها يدوياً وليس عبر النظام تجب الإشارة إلى ذلك). تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>internal, L1, L2, cessation, revenue below 3M, SBR</t>
@@ -4527,42 +4811,58 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Juridical Person Cases</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="I69" s="3" t="inlineStr">
         <is>
           <t>حالات الشخص الاعتباري</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>Dear L2, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review: - The cessation date is as per the trade licence cancellation. - Declaration letter / financial statements have been provided covering all the tax periods up to the cessation date (signed or stamped). - The declaration letter / financial statements for the last period up to the cessation date show no fixed assets recorded. - The taxpayer generated revenue in the tax period {{period}}; however, the taxable income did not reach the AED 375,000 threshold and no tax liability is payable (include all the tax periods of the CT returns). - There is no VAT or Excise Tax history on this TRN / the taxpayer has submitted a VAT deregistration application (to check). - Penalty imposed by {{penaltyBy}} / no penalty to be imposed (to check; if imposed manually and not through the system, mention it). All the above has been checked and the case is clear for L2 review and approval with no tax risk on this taxpayer.</t>
-        </is>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة: - تاريخ التوقف وفقاً لتاريخ إلغاء الرخصة التجارية. - تم تقديم خطاب إقرار / بيانات مالية تغطي جميع الفترات الضريبية حتى تاريخ التوقف (موقعة أو مختومة). - أظهر خطاب الإقرار / البيانات المالية عن الفترة الأخيرة حتى تاريخ التوقف عدم وجود أصول ثابتة مسجلة. - حقق الخاضع للضريبة إيرادات خلال الفترة الضريبية {{period}}، إلا أن الدخل الخاضع للضريبة لم يبلغ حد 375,000 درهم ولا توجد التزامات ضريبية مستحقة (تُدرج جميع الفترات الضريبية لإقرارات ضريبة الشركات). - لا يوجد سجل لضريبة القيمة المضافة أو الضريبة الانتقائية على رقم التسجيل هذا / قدّم الخاضع للضريبة طلب إلغاء التسجيل لضريبة القيمة المضافة (للتحقق). - تم فرض غرامة بواسطة {{penaltyBy}} / لا توجد غرامة مستحقة (للتحقق؛ في حال فرضها يدوياً وليس عبر النظام تجب الإشارة إلى ذلك). تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="3" t="inlineStr"/>
-      <c r="M69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Dear Level 2 reviewer, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review:
+- The cessation date is as per the trade licence cancellation.
+- Declaration letter / financial statements have been provided covering all the tax periods up to the cessation date (signed or stamped).
+- The declaration letter / financial statements for the last period up to the cessation date show no fixed assets recorded.
+- The taxpayer generated revenue in the tax period {{period}}; however, the taxable income did not reach the AED 375,000 threshold and no tax liability is payable (include all the tax periods of the Corporate Tax returns).
+- There is no Value Added Tax (VAT) or Excise Tax history on this Tax Registration Number (TRN) / the taxpayer has submitted a VAT deregistration application (to check).
+- Penalty imposed by {{penaltyBy}} / no penalty to be imposed (to check; if imposed manually and not through the system, mention it). All the above has been checked and the case is clear for Level 2 review and approval with no tax risk on this taxpayer.</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة:
+- تاريخ التوقف وفقاً لتاريخ إلغاء الرخصة التجارية.
+- تم تقديم خطاب إقرار / بيانات مالية تغطي جميع الفترات الضريبية حتى تاريخ التوقف (موقعة أو مختومة).
+- أظهر خطاب الإقرار / البيانات المالية عن الفترة الأخيرة حتى تاريخ التوقف عدم وجود أصول ثابتة مسجلة.
+- حقق الخاضع للضريبة إيرادات خلال الفترة الضريبية {{period}}، إلا أن الدخل الخاضع للضريبة لم يبلغ حد 375,000 درهم ولا توجد التزامات ضريبية مستحقة (تُدرج جميع الفترات الضريبية لإقرارات ضريبة الشركات).
+- لا يوجد سجل لضريبة القيمة المضافة أو الضريبة الانتقائية على رقم التسجيل هذا / قدّم الخاضع للضريبة طلب إلغاء التسجيل لضريبة القيمة المضافة (للتحقق).
+- تم فرض غرامة بواسطة {{penaltyBy}} / لا توجد غرامة مستحقة (للتحقق؛ في حال فرضها يدوياً وليس عبر النظام تجب الإشارة إلى ذلك). تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="3" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>internal, L1, L2, cessation, net profit below 375K, threshold</t>
@@ -4585,42 +4885,54 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Juridical Person Cases</t>
         </is>
       </c>
-      <c r="G70" s="3" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>حالات الشخص الاعتباري</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>Dear L2, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review: - This person should not be registered, as the taxpayer holds another TRN: {{otherTrn}}. - The CT return is submitted under the other TRN; the taxpayer is not required to file under both TRNs, so no return will appear in this application. - No penalties should be imposed. - Confirmation letter that the taxpayer will register for CT (where a system error prevented registration). All the above has been checked and the case is clear for L2 review and approval with no tax risk on this taxpayer.</t>
-        </is>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة: - لا ينبغي تسجيل هذا الشخص، إذ إن الخاضع للضريبة لديه رقم تسجيل ضريبي آخر: {{otherTrn}}. - تم تقديم إقرار ضريبة الشركات على رقم التسجيل الآخر، ولا يُطلب من الخاضع للضريبة التقديم على كلا الرقمين، وبالتالي لن يظهر أي إقرار في هذا الطلب. - لا ينبغي فرض أي غرامات. - خطاب تأكيد بأن الخاضع للضريبة سيقوم بالتسجيل لضريبة الشركات (في حال وجود خطأ في النظام حال دون التسجيل). تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="3" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Dear Level 2 reviewer, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review:
+- This person should not be registered, as the taxpayer holds another Tax Registration Number (TRN): {{otherTrn}}.
+- The Corporate Tax return is submitted under the other TRN; the taxpayer is not required to file under both TRNs, so no return will appear in this application.
+- No penalties should be imposed.
+- Confirmation letter that the taxpayer will register for Corporate Tax (where a system error prevented registration). All the above has been checked and the case is clear for Level 2 review and approval with no tax risk on this taxpayer.</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة:
+- لا ينبغي تسجيل هذا الشخص، إذ إن الخاضع للضريبة لديه رقم تسجيل ضريبي آخر: {{otherTrn}}.
+- تم تقديم إقرار ضريبة الشركات على رقم التسجيل الآخر، ولا يُطلب من الخاضع للضريبة التقديم على كلا الرقمين، وبالتالي لن يظهر أي إقرار في هذا الطلب.
+- لا ينبغي فرض أي غرامات.
+- خطاب تأكيد بأن الخاضع للضريبة سيقوم بالتسجيل لضريبة الشركات (في حال وجود خطأ في النظام حال دون التسجيل). تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="3" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>internal, L1, L2, duplicate TRN</t>
@@ -4643,42 +4955,54 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Juridical Person Cases</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="I71" s="3" t="inlineStr">
         <is>
           <t>حالات الشخص الاعتباري</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>Dear L2, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review: - The cessation date is as per the change of the legal type. - Declaration letter / financial statements have been provided covering the first tax period up to the date of the change of legal type (signed). - No revenue was generated for the period {{period}} and the taxpayer elected for Small Business Relief (include all the periods of the CT returns; check the revenue). - VAT has been deregistered. All the above has been checked and the case is clear for L2 review and approval with no tax risk on this taxpayer.</t>
-        </is>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة: - تاريخ التوقف وفقاً لتاريخ تغيير الشكل القانوني. - تم تقديم خطاب إقرار / بيانات مالية تغطي الفترة الضريبية الأولى حتى تاريخ تغيير الشكل القانوني (موقعة). - لم يتم تحقيق أي إيرادات خلال الفترة {{period}} وقد اختار الخاضع للضريبة إعفاء الأعمال الصغيرة (تُدرج جميع فترات إقرارات ضريبة الشركات مع التحقق من الإيرادات). - تم إلغاء التسجيل لضريبة القيمة المضافة. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="3" t="inlineStr"/>
-      <c r="M71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Dear Level 2 reviewer, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review:
+- The cessation date is as per the change of the legal type.
+- Declaration letter / financial statements have been provided covering the first tax period up to the date of the change of legal type (signed).
+- No revenue was generated for the period {{period}} and the taxpayer elected for Small Business Relief (include all the periods of the Corporate Tax returns; check the revenue).
+- Value Added Tax (VAT) has been deregistered. All the above has been checked and the case is clear for Level 2 review and approval with no tax risk on this taxpayer.</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة:
+- تاريخ التوقف وفقاً لتاريخ تغيير الشكل القانوني.
+- تم تقديم خطاب إقرار / بيانات مالية تغطي الفترة الضريبية الأولى حتى تاريخ تغيير الشكل القانوني (موقعة).
+- لم يتم تحقيق أي إيرادات خلال الفترة {{period}} وقد اختار الخاضع للضريبة إعفاء الأعمال الصغيرة (تُدرج جميع فترات إقرارات ضريبة الشركات مع التحقق من الإيرادات).
+- تم إلغاء التسجيل لضريبة القيمة المضافة. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="3" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>internal, L1, L2, change of legal type, LLC to sole, sale of business</t>
@@ -4701,42 +5025,48 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="G72" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Juridical Person Cases</t>
         </is>
       </c>
-      <c r="G72" s="3" t="inlineStr">
+      <c r="I72" s="3" t="inlineStr">
         <is>
           <t>حالات الشخص الاعتباري</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>Dear L2, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review: - The application should be rejected, as the taxpayer must submit an Amend Taxable Person Details application (sale of business from LLC to LLC without a change of legal type).</t>
-        </is>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة: - يجب رفض الطلب، إذ يتعين على الخاضع للضريبة تقديم طلب تعديل بيانات الخاضع للضريبة (بيع الأعمال من شركة ذات مسؤولية محدودة إلى شركة ذات مسؤولية محدودة دون تغيير الشكل القانوني).</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="3" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Dear Level 2 reviewer, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review:
+- The application should be rejected, as the taxpayer must submit an Amend Taxable Person Details application (sale of business from limited liability company (LLC) to LLC without a change of legal type).</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة:
+- يجب رفض الطلب، إذ يتعين على الخاضع للضريبة تقديم طلب تعديل بيانات الخاضع للضريبة (بيع الأعمال من شركة ذات مسؤولية محدودة إلى شركة ذات مسؤولية محدودة دون تغيير الشكل القانوني).</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="3" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>internal, L1, L2, sale of business, LLC to LLC, reject, AMTP</t>
@@ -4759,42 +5089,56 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Juridical Person Cases</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="I73" s="3" t="inlineStr">
         <is>
           <t>حالات الشخص الاعتباري</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>Dear L2, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review: - The cessation date is as per the board resolution or an official minute of meeting. - The taxpayer confirmed, by attaching a declaration letter, that it has no PE, no nexus in the UAE, no State Sourced Income and no business or business activity in the UAE on behalf of the foreign business. - No revenue was generated for the period {{period}} and the taxpayer elected for Small Business Relief (include all the periods of the CT returns). - There is no VAT or Excise Tax history on this TRN / the taxpayer has submitted a VAT deregistration application (to check). - The certificate of continuity has been attached. All the above has been checked and the case is clear for L2 review and approval with no tax risk on this taxpayer.</t>
-        </is>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة: - تاريخ التوقف وفقاً لقرار مجلس الإدارة أو محضر اجتماع رسمي. - أكد الخاضع للضريبة، من خلال إرفاق خطاب إقرار، عدم وجود منشأة دائمة أو صلة في الدولة، وعدم تحقيق دخل ناشئ في الدولة، وعدم مزاولة أعمال أو نشاط أعمال في الدولة نيابةً عن الأعمال الأجنبية. - لم يتم تحقيق أي إيرادات خلال الفترة {{period}} وقد اختار الخاضع للضريبة إعفاء الأعمال الصغيرة (تُدرج جميع فترات إقرارات ضريبة الشركات). - لا يوجد سجل لضريبة القيمة المضافة أو الضريبة الانتقائية على رقم التسجيل هذا / قدّم الخاضع للضريبة طلب إلغاء التسجيل لضريبة القيمة المضافة (للتحقق). - تم إرفاق شهادة الاستمرارية. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="3" t="inlineStr"/>
-      <c r="M73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>Dear Level 2 reviewer, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review:
+- The cessation date is as per the board resolution or an official minute of meeting.
+- The taxpayer confirmed, by attaching a declaration letter, that it has no Permanent Establishment, no nexus in the UAE, no State Sourced Income and no business or business activity in the UAE on behalf of the foreign business.
+- No revenue was generated for the period {{period}} and the taxpayer elected for Small Business Relief (include all the periods of the Corporate Tax returns).
+- There is no Value Added Tax (VAT) or Excise Tax history on this Tax Registration Number (TRN) / the taxpayer has submitted a VAT deregistration application (to check).
+- The certificate of continuity has been attached. All the above has been checked and the case is clear for Level 2 review and approval with no tax risk on this taxpayer.</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة:
+- تاريخ التوقف وفقاً لقرار مجلس الإدارة أو محضر اجتماع رسمي.
+- أكد الخاضع للضريبة، من خلال إرفاق خطاب إقرار، عدم وجود منشأة دائمة أو صلة في الدولة، وعدم تحقيق دخل ناشئ في الدولة، وعدم مزاولة أعمال أو نشاط أعمال في الدولة نيابةً عن الأعمال الأجنبية.
+- لم يتم تحقيق أي إيرادات خلال الفترة {{period}} وقد اختار الخاضع للضريبة إعفاء الأعمال الصغيرة (تُدرج جميع فترات إقرارات ضريبة الشركات).
+- لا يوجد سجل لضريبة القيمة المضافة أو الضريبة الانتقائية على رقم التسجيل هذا / قدّم الخاضع للضريبة طلب إلغاء التسجيل لضريبة القيمة المضافة (للتحقق).
+- تم إرفاق شهادة الاستمرارية. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="3" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>internal, L1, L2, re-domiciliation, continuity</t>
@@ -4817,42 +5161,54 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="G74" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Juridical Person Cases</t>
         </is>
       </c>
-      <c r="G74" s="3" t="inlineStr">
+      <c r="I74" s="3" t="inlineStr">
         <is>
           <t>حالات الشخص الاعتباري</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>Dear L2, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review: - The cessation date is as per the board resolution. - The taxpayer confirmed, by attaching a declaration letter, that it has no PE, no nexus in the UAE, no State Sourced Income and no business or business activity in the UAE on behalf of the foreign business. - No revenue was generated for the period {{period}} and the taxpayer elected for Small Business Relief (include all the periods of the CT returns). - There is no VAT history on this TRN / the taxpayer has submitted a VAT deregistration application (to check). All the above has been checked and the case is clear for L2 review and approval with no tax risk on this taxpayer.</t>
-        </is>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة: - تاريخ التوقف وفقاً لقرار مجلس الإدارة. - أكد الخاضع للضريبة، من خلال إرفاق خطاب إقرار، عدم وجود منشأة دائمة أو صلة في الدولة، وعدم تحقيق دخل ناشئ في الدولة، وعدم مزاولة أعمال أو نشاط أعمال في الدولة نيابةً عن الأعمال الأجنبية. - لم يتم تحقيق أي إيرادات خلال الفترة {{period}} وقد اختار الخاضع للضريبة إعفاء الأعمال الصغيرة (تُدرج جميع فترات إقرارات ضريبة الشركات). - لا يوجد سجل لضريبة القيمة المضافة على رقم التسجيل هذا / قدّم الخاضع للضريبة طلب إلغاء التسجيل لضريبة القيمة المضافة (للتحقق). تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="3" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Dear Level 2 reviewer, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review:
+- The cessation date is as per the board resolution.
+- The taxpayer confirmed, by attaching a declaration letter, that it has no Permanent Establishment, no nexus in the UAE, no State Sourced Income and no business or business activity in the UAE on behalf of the foreign business.
+- No revenue was generated for the period {{period}} and the taxpayer elected for Small Business Relief (include all the periods of the Corporate Tax returns).
+- There is no Value Added Tax (VAT) history on this Tax Registration Number (TRN) / the taxpayer has submitted a VAT deregistration application (to check). All the above has been checked and the case is clear for Level 2 review and approval with no tax risk on this taxpayer.</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة:
+- تاريخ التوقف وفقاً لقرار مجلس الإدارة.
+- أكد الخاضع للضريبة، من خلال إرفاق خطاب إقرار، عدم وجود منشأة دائمة أو صلة في الدولة، وعدم تحقيق دخل ناشئ في الدولة، وعدم مزاولة أعمال أو نشاط أعمال في الدولة نيابةً عن الأعمال الأجنبية.
+- لم يتم تحقيق أي إيرادات خلال الفترة {{period}} وقد اختار الخاضع للضريبة إعفاء الأعمال الصغيرة (تُدرج جميع فترات إقرارات ضريبة الشركات).
+- لا يوجد سجل لضريبة القيمة المضافة على رقم التسجيل هذا / قدّم الخاضع للضريبة طلب إلغاء التسجيل لضريبة القيمة المضافة (للتحقق). تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="3" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>internal, L1, L2, offshore, no trade licence, cessation</t>
@@ -4875,42 +5231,48 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Juridical Person Cases</t>
         </is>
       </c>
-      <c r="G75" s="3" t="inlineStr">
+      <c r="I75" s="3" t="inlineStr">
         <is>
           <t>حالات الشخص الاعتباري</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>Dear L2, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review: - The taxpayer is a Qualifying Public Benefit Entity and is therefore not required to register or to file a CT return. All the above has been checked and the case is clear for L2 review and approval with no tax risk on this taxpayer.</t>
-        </is>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة: - الخاضع للضريبة جهة نفع عام مؤهلة، وبالتالي غير مطالب بالتسجيل أو بتقديم إقرار ضريبة الشركات. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="3" t="inlineStr"/>
-      <c r="M75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Dear Level 2 reviewer, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review:
+- The taxpayer is a Qualifying Public Benefit Entity and is therefore not required to register or to file a Corporate Tax return. All the above has been checked and the case is clear for Level 2 review and approval with no tax risk on this taxpayer.</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة:
+- الخاضع للضريبة جهة نفع عام مؤهلة، وبالتالي غير مطالب بالتسجيل أو بتقديم إقرار ضريبة الشركات. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="3" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>internal, L1, L2, QPBE, public benefit</t>
@@ -4933,42 +5295,48 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="G76" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Juridical Person Cases</t>
         </is>
       </c>
-      <c r="G76" s="3" t="inlineStr">
+      <c r="I76" s="3" t="inlineStr">
         <is>
           <t>حالات الشخص الاعتباري</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>Dear L2, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review: - The taxpayer is an Exempt Person for CT purposes (Government Entity / Government Controlled Entity), and no return is required.</t>
-        </is>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة: - الخاضع للضريبة شخص مُعفى من ضريبة الشركات بصفته (جهة حكومية / جهة خاضعة لسيطرة الحكومة)، ولا يُطلب منه تقديم إقرار.</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="3" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Dear Level 2 reviewer, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review:
+- The taxpayer is an Exempt Person for Corporate Tax purposes (Government Entity / Government Controlled Entity), and no return is required.</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة:
+- الخاضع للضريبة شخص مُعفى من ضريبة الشركات بصفته (جهة حكومية / جهة خاضعة لسيطرة الحكومة)، ولا يُطلب منه تقديم إقرار.</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="3" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>internal, L1, L2, exempt person, government</t>
@@ -4991,42 +5359,54 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Juridical Person Cases</t>
         </is>
       </c>
-      <c r="G77" s="3" t="inlineStr">
+      <c r="I77" s="3" t="inlineStr">
         <is>
           <t>حالات الشخص الاعتباري</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>Dear L2, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review: - The taxpayer is not required to register for CT. - The taxpayer shared the notification form from the Ministry of Finance. - The taxpayer is subject to tax at the Emirate level. - Financial statements were shared and all the income was generated from the Extractive Business. All the above has been checked and the case is clear for L2 review and approval with no tax risk on this taxpayer.</t>
-        </is>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة: - الخاضع للضريبة غير مطالب بالتسجيل لضريبة الشركات. - قدّم الخاضع للضريبة نموذج الإخطار الصادر عن وزارة المالية. - الخاضع للضريبة يخضع للضريبة على مستوى الإمارة. - تم تقديم البيانات المالية، وجميع الدخل ناتج عن الأعمال الاستخراجية. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="3" t="inlineStr"/>
-      <c r="M77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>Dear Level 2 reviewer, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review:
+- The taxpayer is not required to register for Corporate Tax.
+- The taxpayer shared the notification form from the Ministry of Finance.
+- The taxpayer is subject to tax at the Emirate level.
+- Financial statements were shared and all the income was generated from the Extractive Business. All the above has been checked and the case is clear for Level 2 review and approval with no tax risk on this taxpayer.</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة:
+- الخاضع للضريبة غير مطالب بالتسجيل لضريبة الشركات.
+- قدّم الخاضع للضريبة نموذج الإخطار الصادر عن وزارة المالية.
+- الخاضع للضريبة يخضع للضريبة على مستوى الإمارة.
+- تم تقديم البيانات المالية، وجميع الدخل ناتج عن الأعمال الاستخراجية. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="3" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>internal, L1, L2, extractive, natural resource, MoF</t>
@@ -5049,42 +5429,54 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="G78" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Juridical Person Cases</t>
         </is>
       </c>
-      <c r="G78" s="3" t="inlineStr">
+      <c r="I78" s="3" t="inlineStr">
         <is>
           <t>حالات الشخص الاعتباري</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>Dear L2, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review: - The taxpayer is not required to register for CT. - The taxpayer shared the confirmation letter from the Ministry of Finance. - The taxpayer is subject to tax at the Emirate level. - Financial statements were shared and all the income was generated from the Non-Extractive Natural Resource Business. All the above has been checked and the case is clear for L2 review and approval with no tax risk on this taxpayer.</t>
-        </is>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة: - الخاضع للضريبة غير مطالب بالتسجيل لضريبة الشركات. - قدّم الخاضع للضريبة خطاب التأكيد الصادر عن وزارة المالية. - الخاضع للضريبة يخضع للضريبة على مستوى الإمارة. - تم تقديم البيانات المالية، وجميع الدخل ناتج عن أعمال الموارد الطبيعية غير الاستخراجية. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="3" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Dear Level 2 reviewer, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review:
+- The taxpayer is not required to register for Corporate Tax.
+- The taxpayer shared the confirmation letter from the Ministry of Finance.
+- The taxpayer is subject to tax at the Emirate level.
+- Financial statements were shared and all the income was generated from the Non-Extractive Natural Resource Business. All the above has been checked and the case is clear for Level 2 review and approval with no tax risk on this taxpayer.</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة:
+- الخاضع للضريبة غير مطالب بالتسجيل لضريبة الشركات.
+- قدّم الخاضع للضريبة خطاب التأكيد الصادر عن وزارة المالية.
+- الخاضع للضريبة يخضع للضريبة على مستوى الإمارة.
+- تم تقديم البيانات المالية، وجميع الدخل ناتج عن أعمال الموارد الطبيعية غير الاستخراجية. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="3" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>internal, L1, L2, non-extractive, natural resource, MoF</t>
@@ -5107,42 +5499,50 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E79" s="3" t="inlineStr">
+      <c r="G79" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Juridical Person Cases</t>
         </is>
       </c>
-      <c r="G79" s="3" t="inlineStr">
+      <c r="I79" s="3" t="inlineStr">
         <is>
           <t>حالات الشخص الاعتباري</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>Dear L2, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review: - The cessation date is as per the board resolution. - Confirmation letter that both partners hold TRNs and that the income is reported / will be reported in their returns. All the above has been checked and the case is clear for L2 review and approval with no tax risk on this taxpayer.</t>
-        </is>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة: - تاريخ التوقف وفقاً لقرار مجلس الإدارة. - خطاب تأكيد بأن كلا الشريكين لديهما أرقام تسجيل ضريبي وأن الدخل تم الإفصاح عنه / سيتم الإفصاح عنه في إقراراتهما. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="3" t="inlineStr"/>
-      <c r="M79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>Dear Level 2 reviewer, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review:
+- The cessation date is as per the board resolution.
+- Confirmation letter that both partners hold TRNs and that the income is reported / will be reported in their returns. All the above has been checked and the case is clear for Level 2 review and approval with no tax risk on this taxpayer.</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة:
+- تاريخ التوقف وفقاً لقرار مجلس الإدارة.
+- خطاب تأكيد بأن كلا الشريكين لديهما أرقام تسجيل ضريبي وأن الدخل تم الإفصاح عنه / سيتم الإفصاح عنه في إقراراتهما. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="3" t="inlineStr"/>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>internal, L1, L2, unincorporated partnership</t>
@@ -5165,42 +5565,52 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr">
+      <c r="G80" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Juridical Person Cases</t>
         </is>
       </c>
-      <c r="G80" s="3" t="inlineStr">
+      <c r="I80" s="3" t="inlineStr">
         <is>
           <t>حالات الشخص الاعتباري</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>Dear L2, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review: - The cessation date is as per the publication date of the Cabinet Decision. - No revenue was generated for the period {{period}} and the taxpayer elected for Small Business Relief (include all the periods of the CT returns). - The mandated activities of the taxpayer are as per the Cabinet Decision. All the above has been checked and the case is clear for L2 review and approval with no tax risk on this taxpayer.</t>
-        </is>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة: - تاريخ التوقف وفقاً لتاريخ نشر قرار مجلس الوزراء. - لم يتم تحقيق أي إيرادات خلال الفترة {{period}} وقد اختار الخاضع للضريبة إعفاء الأعمال الصغيرة (تُدرج جميع فترات إقرارات ضريبة الشركات). - الأنشطة المكلّف بها الخاضع للضريبة وفقاً لقرار مجلس الوزراء. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="3" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Dear Level 2 reviewer, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review:
+- The cessation date is as per the publication date of the Cabinet Decision.
+- No revenue was generated for the period {{period}} and the taxpayer elected for Small Business Relief (include all the periods of the Corporate Tax returns).
+- The mandated activities of the taxpayer are as per the Cabinet Decision. All the above has been checked and the case is clear for Level 2 review and approval with no tax risk on this taxpayer.</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة:
+- تاريخ التوقف وفقاً لتاريخ نشر قرار مجلس الوزراء.
+- لم يتم تحقيق أي إيرادات خلال الفترة {{period}} وقد اختار الخاضع للضريبة إعفاء الأعمال الصغيرة (تُدرج جميع فترات إقرارات ضريبة الشركات).
+- الأنشطة المكلّف بها الخاضع للضريبة وفقاً لقرار مجلس الوزراء. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="3" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>internal, L1, L2, cabinet decision, mandated entity</t>
@@ -5223,42 +5633,54 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E81" s="3" t="inlineStr">
+      <c r="G81" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Natural Person Cases</t>
         </is>
       </c>
-      <c r="G81" s="3" t="inlineStr">
+      <c r="I81" s="3" t="inlineStr">
         <is>
           <t>حالات الشخص الطبيعي</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>Dear L2, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review: - Declaration letter / financial statements / turnover declaration have been provided covering all the tax periods (signed). - Total revenue is below the AED 1 million threshold and the taxpayer can be deregistered. - Confirmation letter that the owner does not hold any other TRNs has been attached and confirmed by the taxpayer. - No final return is required. All the above has been checked and the case is clear for L2 review and approval with no tax risk on this taxpayer.</t>
-        </is>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة: - تم تقديم خطاب إقرار / بيانات مالية / إقرار بحجم الأعمال يغطي جميع الفترات الضريبية (موقع). - إجمالي الإيرادات أقل من حد المليون درهم، ويمكن إلغاء تسجيل الخاضع للضريبة. - تم إرفاق خطاب تأكيد بعدم وجود أي أرقام تسجيل ضريبي أخرى للمالك، وتم تأكيده من قبل الخاضع للضريبة. - لا يُطلب تقديم إقرار نهائي. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="3" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Dear Level 2 reviewer, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review:
+- Declaration letter / financial statements / turnover declaration have been provided covering all the tax periods (signed).
+- Total revenue is below the AED 1 million threshold and the taxpayer can be deregistered.
+- Confirmation letter that the owner does not hold any other TRNs has been attached and confirmed by the taxpayer.
+- No final return is required. All the above has been checked and the case is clear for Level 2 review and approval with no tax risk on this taxpayer.</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة:
+- تم تقديم خطاب إقرار / بيانات مالية / إقرار بحجم الأعمال يغطي جميع الفترات الضريبية (موقع).
+- إجمالي الإيرادات أقل من حد المليون درهم، ويمكن إلغاء تسجيل الخاضع للضريبة.
+- تم إرفاق خطاب تأكيد بعدم وجود أي أرقام تسجيل ضريبي أخرى للمالك، وتم تأكيده من قبل الخاضع للضريبة.
+- لا يُطلب تقديم إقرار نهائي. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="3" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>internal, L1, L2, natural person, below 1 million</t>
@@ -5281,42 +5703,58 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E82" s="3" t="inlineStr">
+      <c r="G82" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Natural Person Cases</t>
         </is>
       </c>
-      <c r="G82" s="3" t="inlineStr">
+      <c r="I82" s="3" t="inlineStr">
         <is>
           <t>حالات الشخص الطبيعي</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>Dear L2, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review: - The cessation date is as per the MOA. - Declaration letter / financial statements have been provided covering the first tax period up to the date of the change of legal type (signed). - No revenue was generated for the period {{period}} and the taxpayer elected for Small Business Relief (include all the periods of the CT returns; check the revenue). - Confirmation letter that the owner does not hold any other TRNs and is not conducting any business has been attached and confirmed by the taxpayer. - The CT certificate of the new company (LLC) has been attached. - VAT has been deregistered. All the above has been checked and the case is clear for L2 review and approval with no tax risk on this taxpayer.</t>
-        </is>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة: - تاريخ التوقف وفقاً لعقد التأسيس. - تم تقديم خطاب إقرار / بيانات مالية تغطي الفترة الضريبية الأولى حتى تاريخ تغيير الشكل القانوني (موقعة). - لم يتم تحقيق أي إيرادات خلال الفترة {{period}} وقد اختار الخاضع للضريبة إعفاء الأعمال الصغيرة (تُدرج جميع فترات إقرارات ضريبة الشركات مع التحقق من الإيرادات). - تم إرفاق خطاب تأكيد بعدم وجود أي أرقام تسجيل ضريبي أخرى للمالك وعدم مزاولته أي أعمال، وتم تأكيده من قبل الخاضع للضريبة. - تم إرفاق شهادة ضريبة الشركات للشركة الجديدة (ذات المسؤولية المحدودة). - تم إلغاء التسجيل لضريبة القيمة المضافة. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="3" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Dear Level 2 reviewer, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review:
+- The cessation date is as per the Memorandum of Association.
+- Declaration letter / financial statements have been provided covering the first tax period up to the date of the change of legal type (signed).
+- No revenue was generated for the period {{period}} and the taxpayer elected for Small Business Relief (include all the periods of the Corporate Tax returns; check the revenue).
+- Confirmation letter that the owner does not hold any other TRNs and is not conducting any business has been attached and confirmed by the taxpayer.
+- The Corporate Tax registration certificate of the new company (LLC) has been attached.
+- Value Added Tax (VAT) has been deregistered. All the above has been checked and the case is clear for Level 2 review and approval with no tax risk on this taxpayer.</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة:
+- تاريخ التوقف وفقاً لعقد التأسيس.
+- تم تقديم خطاب إقرار / بيانات مالية تغطي الفترة الضريبية الأولى حتى تاريخ تغيير الشكل القانوني (موقعة).
+- لم يتم تحقيق أي إيرادات خلال الفترة {{period}} وقد اختار الخاضع للضريبة إعفاء الأعمال الصغيرة (تُدرج جميع فترات إقرارات ضريبة الشركات مع التحقق من الإيرادات).
+- تم إرفاق خطاب تأكيد بعدم وجود أي أرقام تسجيل ضريبي أخرى للمالك وعدم مزاولته أي أعمال، وتم تأكيده من قبل الخاضع للضريبة.
+- تم إرفاق شهادة ضريبة الشركات للشركة الجديدة (ذات المسؤولية المحدودة).
+- تم إلغاء التسجيل لضريبة القيمة المضافة. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>internal, L1, L2, natural person, sole to LLC, change of legal type, sale of business</t>
@@ -5339,42 +5777,54 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E83" s="3" t="inlineStr">
+      <c r="G83" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Natural Person Cases</t>
         </is>
       </c>
-      <c r="G83" s="3" t="inlineStr">
+      <c r="I83" s="3" t="inlineStr">
         <is>
           <t>حالات الشخص الطبيعي</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>Dear L2, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review: - The cessation date is as per the death certificate. - Confirmation letter that the owner was not conducting any business and was not registered with the FTA under their name in the UAE has been attached and confirmed. - Declaration letter / financial statements / turnover declaration have been provided covering the first tax period and the {{period}} tax period (signed). - Confirmation letter that the heirs will not continue the business has been attached. All the above has been checked and the case is clear for L2 review and approval with no tax risk on this taxpayer.</t>
-        </is>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة: - تاريخ التوقف وفقاً لشهادة الوفاة. - تم إرفاق خطاب تأكيد بعدم مزاولة المالك أي أعمال وعدم تسجيله لدى الهيئة الاتحادية للضرائب باسمه في الدولة، وتم تأكيده. - تم تقديم خطاب إقرار / بيانات مالية / إقرار بحجم الأعمال يغطي الفترة الضريبية الأولى والفترة الضريبية {{period}} (موقع). - تم إرفاق خطاب تأكيد بأن الورثة لن يستمروا في مزاولة الأعمال. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="3" t="inlineStr"/>
-      <c r="M83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>Dear Level 2 reviewer, as per the attachments the taxpayer has provided the necessary documents; I have checked them and noted the below for your kind review:
+- The cessation date is as per the death certificate.
+- Confirmation letter that the owner was not conducting any business and was not registered with the Federal Tax Authority (FTA) under their name in the UAE has been attached and confirmed.
+- Declaration letter / financial statements / turnover declaration have been provided covering the first tax period and the {{period}} tax period (signed).
+- Confirmation letter that the heirs will not continue the business has been attached. All the above has been checked and the case is clear for Level 2 review and approval with no tax risk on this taxpayer.</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>إلى مراجع المستوى الثاني، بناءً على المرفقات قدّم الخاضع للضريبة المستندات اللازمة، وقد تم التحقق منها ورصد الملاحظات التالية للمراجعة الكريمة:
+- تاريخ التوقف وفقاً لشهادة الوفاة.
+- تم إرفاق خطاب تأكيد بعدم مزاولة المالك أي أعمال وعدم تسجيله لدى الهيئة الاتحادية للضرائب باسمه في الدولة، وتم تأكيده.
+- تم تقديم خطاب إقرار / بيانات مالية / إقرار بحجم الأعمال يغطي الفترة الضريبية الأولى والفترة الضريبية {{period}} (موقع).
+- تم إرفاق خطاب تأكيد بأن الورثة لن يستمروا في مزاولة الأعمال. تم التحقق من جميع ما ورد أعلاه، والحالة جاهزة لمراجعة واعتماد المستوى الثاني دون أي مخاطر ضريبية على هذا الخاضع للضريبة.</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="3" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>internal, L1, L2, natural person, death</t>
@@ -5397,42 +5847,46 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E84" s="3" t="inlineStr">
+      <c r="G84" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Fast Track &amp; Approval</t>
         </is>
       </c>
-      <c r="G84" s="3" t="inlineStr">
+      <c r="I84" s="3" t="inlineStr">
         <is>
           <t>المسار السريع والاعتماد</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>The application has been reviewed under the Fast-Track Process, which is designed to expedite eligible CT deregistration applications through a simplified review. The review included: verifying that the trade licence cancellation date matches the date of cessation; confirming that the tax amount is AED 0 in the submitted returns; and performing a high-level review of the submitted financial statements, including revenue below AED 3 million, net profit below AED 375,000, and a balance sheet check with no risks identified. Based on the above review, no material risks were identified; therefore, no detailed review of the Corporate Tax return or of the VAT deregistration status was performed under the Fast-Track Process by L1.</t>
-        </is>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>The application has been reviewed under the Fast-Track Process, which is designed to expedite eligible Corporate Tax deregistration applications through a simplified review. The review included: verifying that the trade licence cancellation date matches the date of cessation; confirming that the tax amount is AED 0 in the submitted returns; and performing a high-level review of the submitted financial statements, including revenue below AED 3 million, net profit below AED 375,000, and a balance sheet check with no risks identified. Based on the above review, no material risks were identified; therefore, no detailed review of the Corporate Tax return or of the Value Added Tax (VAT) deregistration status was performed under the Fast-Track Process by the Level 1 reviewer.</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
         <is>
           <t>تمت مراجعة الطلب ضمن إجراءات المسار السريع التي تهدف إلى تسريع طلبات إلغاء التسجيل المؤهلة لضريبة الشركات من خلال مراجعة مبسطة. شملت المراجعة: التحقق من تطابق تاريخ إلغاء الرخصة التجارية مع تاريخ التوقف؛ والتأكد من أن مبلغ الضريبة صفر درهم في الإقرارات المقدمة؛ وإجراء مراجعة عالية المستوى للقوائم المالية المقدمة بما في ذلك إيرادات أقل من 3 ملايين درهم وصافي ربح أقل من 375,000 درهم ومراجعة الميزانية العمومية دون تحديد أي مخاطر. وبناءً على ما سبق لم يتم تحديد أي مخاطر جوهرية، وعليه لم يتم إجراء مراجعة تفصيلية لإقرار ضريبة الشركات أو لحالة إلغاء التسجيل في ضريبة القيمة المضافة ضمن المسار السريع من قبل المستوى الأول.</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="3" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="3" t="inlineStr"/>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>internal, fast track, L1, simplified review</t>
@@ -5455,42 +5909,46 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E85" s="3" t="inlineStr">
+      <c r="G85" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Fast Track &amp; Approval</t>
         </is>
       </c>
-      <c r="G85" s="3" t="inlineStr">
+      <c r="I85" s="3" t="inlineStr">
         <is>
           <t>المسار السريع والاعتماد</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>Under the Fast-Track Process, the check covered verifying the trade licence cancellation date, the financial statements including the balance sheet and profit and loss, that the tax amounts are zero (no detailed return review), and that there is no late CT deregistration penalty. Approved.</t>
-        </is>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>Under the Fast-Track Process, the check covered verifying the trade licence cancellation date, the financial statements including the balance sheet and profit and loss, that the tax amounts are zero (no detailed return review), and that there is no late Corporate Tax deregistration penalty. Approved.</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
         <is>
           <t>ضمن إجراءات المسار السريع، شملت المراجعة التحقق من تاريخ إلغاء الرخصة التجارية، ومراجعة القوائم المالية بما في ذلك الميزانية العمومية وقائمة الأرباح والخسائر، والتأكد من أن مبالغ الضريبة تساوي صفراً (دون مراجعة تفصيلية للإقرار)، والتأكد من عدم وجود غرامة تأخير على إلغاء التسجيل لضريبة الشركات. تمت الموافقة.</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="3" t="inlineStr"/>
-      <c r="M85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="3" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>internal, fast track, L2, approved</t>
@@ -5513,42 +5971,56 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E86" s="3" t="inlineStr">
+      <c r="G86" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Fast Track &amp; Approval</t>
         </is>
       </c>
-      <c r="G86" s="3" t="inlineStr">
+      <c r="I86" s="3" t="inlineStr">
         <is>
           <t>المسار السريع والاعتماد</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>Fully checked: 1) the cessation date matches the trade licence cancellation date; 2) the CT returns for the periods up to the cessation date have been submitted; 3) the trade licence cancellation and the financial statements are both attached; 4) no VAT history / VAT deregistration approved; 5) no / AED {{penaltyAmount}} CT deregistration penalty imposed. Approved.</t>
-        </is>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>تم التحقق بالكامل: 1) تاريخ التوقف مطابق لتاريخ إلغاء الرخصة التجارية؛ 2) تم تقديم إقرارات ضريبة الشركات عن الفترات حتى تاريخ التوقف؛ 3) تم إرفاق إلغاء الرخصة التجارية والبيانات المالية؛ 4) لا يوجد سجل لضريبة القيمة المضافة / تمت الموافقة على إلغاء تسجيلها؛ 5) لا توجد / تم فرض غرامة إلغاء تسجيل لضريبة الشركات بقيمة {{penaltyAmount}} درهم. تمت الموافقة.</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="3" t="inlineStr"/>
-      <c r="M86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>Fully checked:
+1) the cessation date matches the trade licence cancellation date
+2) the Corporate Tax returns for the periods up to the cessation date have been submitted
+3) the trade licence cancellation and the financial statements are both attached
+4) no Value Added Tax (VAT) history / VAT deregistration approved
+5) no / AED {{penaltyAmount}} Corporate Tax deregistration penalty imposed. Approved.</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>تم التحقق بالكامل:
+1) تاريخ التوقف مطابق لتاريخ إلغاء الرخصة التجارية
+2) تم تقديم إقرارات ضريبة الشركات عن الفترات حتى تاريخ التوقف
+3) تم إرفاق إلغاء الرخصة التجارية والبيانات المالية
+4) لا يوجد سجل لضريبة القيمة المضافة / تمت الموافقة على إلغاء تسجيلها
+5) لا توجد / تم فرض غرامة إلغاء تسجيل لضريبة الشركات بقيمة {{penaltyAmount}} درهم. تمت الموافقة.</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="3" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>internal, L2, approval, fully checked</t>
@@ -5571,42 +6043,46 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E87" s="3" t="inlineStr">
+      <c r="G87" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>L1 Rejection Reasons</t>
         </is>
       </c>
-      <c r="G87" s="3" t="inlineStr">
+      <c r="I87" s="3" t="inlineStr">
         <is>
           <t>أسباب الرفض (المستوى الأول)</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>L1 rejection reason: the submitted Corporate Tax registration details are incorrect and do not comply with the registration guidelines; the taxpayer should correct them through Amend Taxable Person Details / Change Entity Type.</t>
-        </is>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>Level 1 rejection reason: the submitted Corporate Tax registration details are incorrect and do not comply with the registration guidelines; the taxpayer should correct them through Amend Taxable Person Details / Change Entity Type.</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
         <is>
           <t>سبب الرفض (المستوى الأول): بيانات تسجيل ضريبة الشركات المقدمة غير صحيحة ولا تتوافق مع إرشادات التسجيل؛ يتعين على الخاضع للضريبة تصحيحها من خلال تعديل بيانات الخاضع للضريبة / تغيير نوع الكيان.</t>
         </is>
       </c>
-      <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="3" t="inlineStr"/>
-      <c r="M87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>internal, L1, reject, wrong registration</t>
@@ -5629,42 +6105,46 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E88" s="3" t="inlineStr">
+      <c r="G88" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>L1 Rejection Reasons</t>
         </is>
       </c>
-      <c r="G88" s="3" t="inlineStr">
+      <c r="I88" s="3" t="inlineStr">
         <is>
           <t>أسباب الرفض (المستوى الأول)</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>L1 rejection reason: the business was sold without a change in legal type or ownership, which requires an Amend Taxable Person Details application.</t>
-        </is>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>Level 1 rejection reason: the business was sold without a change in legal type or ownership, which requires an Amend Taxable Person Details application.</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
         <is>
           <t>سبب الرفض (المستوى الأول): بيعت الأعمال دون تغيير في الشكل القانوني أو الملكية، وهو ما يستوجب تقديم طلب تعديل بيانات الخاضع للضريبة.</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="3" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="3" t="inlineStr"/>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>internal, L1, reject, sale of business</t>
@@ -5687,42 +6167,46 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E89" s="3" t="inlineStr">
+      <c r="G89" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>L1 Rejection Reasons</t>
         </is>
       </c>
-      <c r="G89" s="3" t="inlineStr">
+      <c r="I89" s="3" t="inlineStr">
         <is>
           <t>أسباب الرفض (المستوى الأول)</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>L1 rejection reason: the required documents were not submitted despite multiple requests.</t>
-        </is>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>Level 1 rejection reason: the required documents were not submitted despite multiple requests.</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
         <is>
           <t>سبب الرفض (المستوى الأول): لم تُقدَّم المستندات المطلوبة رغم الطلبات المتكررة.</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="3" t="inlineStr"/>
-      <c r="M89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>internal, L1, reject, documents</t>
@@ -5745,42 +6229,46 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E90" s="3" t="inlineStr">
+      <c r="G90" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>L1 Rejection Reasons</t>
         </is>
       </c>
-      <c r="G90" s="3" t="inlineStr">
+      <c r="I90" s="3" t="inlineStr">
         <is>
           <t>أسباب الرفض (المستوى الأول)</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>L1 rejection reason: the applicant is listed in Cabinet Decision No. 37 of 2023 and must remain registered and submit the annual declaration.</t>
-        </is>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>Level 1 rejection reason: the applicant is listed in Cabinet Decision No. 37 of 2023 and must remain registered and submit the annual declaration.</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
         <is>
           <t>سبب الرفض (المستوى الأول): مقدم الطلب مدرج في قرار مجلس الوزراء رقم (37) لسنة 2023، ويتعين عليه البقاء مسجلاً وتقديم الإقرار السنوي.</t>
         </is>
       </c>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="3" t="inlineStr"/>
-      <c r="M90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="3" t="inlineStr"/>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>internal, L1, reject, QPBE</t>
@@ -5803,42 +6291,46 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E91" s="3" t="inlineStr">
+      <c r="G91" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>L1 Rejection Reasons</t>
         </is>
       </c>
-      <c r="G91" s="3" t="inlineStr">
+      <c r="I91" s="3" t="inlineStr">
         <is>
           <t>أسباب الرفض (المستوى الأول)</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>L1 rejection reason: the taxpayer is not eligible to deregister the TRN while the trade licence is frozen; the licence must be cancelled to proceed.</t>
-        </is>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>Level 1 rejection reason: the taxpayer is not eligible to deregister the Tax Registration Number (TRN) while the trade licence is frozen; the licence must be cancelled to proceed.</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
         <is>
           <t>سبب الرفض (المستوى الأول): الخاضع للضريبة غير مؤهل لإلغاء تسجيل رقم التسجيل الضريبي ما دامت الرخصة التجارية مجمّدة؛ يجب إلغاء الرخصة للمضي في الإلغاء.</t>
         </is>
       </c>
-      <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="3" t="inlineStr"/>
-      <c r="M91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="3" t="inlineStr"/>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>internal, L1, reject, frozen licence</t>
@@ -5861,42 +6353,46 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Internal note</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
           <t>Internal Review Notes (L1 → L2)</t>
         </is>
       </c>
-      <c r="E92" s="3" t="inlineStr">
+      <c r="G92" s="3" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة الداخلية (المستوى 1 ← 2)</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>L1 Rejection Reasons</t>
         </is>
       </c>
-      <c r="G92" s="3" t="inlineStr">
+      <c r="I92" s="3" t="inlineStr">
         <is>
           <t>أسباب الرفض (المستوى الأول)</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>Internal note</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>L1 rejection reason: the natural person reported revenue exceeding AED 1 million; deregistration is not permitted under the applicable guidelines.</t>
-        </is>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>Level 1 rejection reason: the natural person reported revenue exceeding AED 1 million; deregistration is not permitted under the applicable guidelines.</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
         <is>
           <t>سبب الرفض (المستوى الأول): أفصح الشخص الطبيعي عن إيرادات تتجاوز مليون درهم؛ لا يُسمح بإلغاء التسجيل وفقاً للإرشادات المعمول بها.</t>
         </is>
       </c>
-      <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="3" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="3" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>internal, L1, reject, natural person, 1 million</t>
@@ -5917,7 +6413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5925,17 +6421,13 @@
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="46" customWidth="1" min="11" max="11"/>
-    <col width="46" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -5958,45 +6450,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Basis (EN)</t>
+          <t>Basis / outcome</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Basis (AR)</t>
+          <t>Documents required</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Documents required (EN)</t>
+          <t>Eligible date</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Documents required (AR)</t>
+          <t>Reviewer checks</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Eligible date (EN)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Eligible date (AR)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Reviewer checks (EN)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Reviewer checks (AR)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Comments used</t>
         </is>
@@ -6026,46 +6498,24 @@
           <t>Business no longer making taxable supplies</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>النشاط لم يعد يقدم توريدات خاضعة للضريبة</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>• Cancellation certificate from the issuing authority
 • Financial declaration from registration date until today (can be checked from Taxpayer Overview)
 • Declaration of sole establishments owned, if the entity is a sole establishment (check the owner from the ID number)</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>• شهادة الإلغاء من جهة الإصدار
-• بيان مالي من تاريخ التسجيل حتى اليوم (يمكن التحقق منه من ملخص الخاضع للضريبة)
-• إقرار بالمؤسسات الفردية المملوكة إذا كان الكيان مؤسسة فردية (تحقق من المالك عبر رقم الهوية)</t>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Whichever is earlier: the turnover date or the cancellation date</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>• If not yet cancelled or liquidated: board resolution and last taxable invoice</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Whichever is earlier: the turnover date or the cancellation date</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>الأسبق بين تاريخ حجم الأعمال وتاريخ الإلغاء</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>• If not yet cancelled or liquidated: board resolution and last taxable invoice</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>• إذا لم يتم الإلغاء أو التصفية بعد: قرار مجلس الإدارة وآخر فاتورة ضريبية</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>lc-01, cm-01, cm-02</t>
         </is>
@@ -6095,38 +6545,20 @@
           <t>Business no longer making taxable supplies</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>النشاط لم يعد يقدم توريدات خاضعة للضريبة</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>• Freezing document or letter from the issuing authority
 • Financial declaration from registration date until today (can be checked from Taxpayer Overview)
 • Declaration of sole establishments owned, if the entity is a sole establishment (check the owner from the ID number)</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>• مستند أو خطاب التجميد من جهة الإصدار
-• بيان مالي من تاريخ التسجيل حتى اليوم (يمكن التحقق منه من ملخص الخاضع للضريبة)
-• إقرار بالمؤسسات الفردية المملوكة إذا كان الكيان مؤسسة فردية (تحقق من المالك عبر رقم الهوية)</t>
-        </is>
-      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Whichever is earlier: the turnover date or the freezing date</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Whichever is earlier: the turnover date or the freezing date</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>الأسبق بين تاريخ حجم الأعمال وتاريخ التجميد</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>lc-02, cm-01, cm-02</t>
         </is>
@@ -6156,12 +6588,7 @@
           <t>Business no longer making taxable supplies</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>النشاط لم يعد يقدم توريدات خاضعة للضريبة</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>• MOA or contract evidencing the change in legal status
 • Previous and current trade licence
@@ -6169,27 +6596,13 @@
 • Declaration of sole establishments owned, if the entity is a sole establishment (check the owner from the ID number)</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>• عقد التأسيس أو العقد المثبت لتغيير الشكل القانوني
-• الرخصة التجارية السابقة والحالية
-• بيان مالي من تاريخ التسجيل حتى اليوم (يمكن التحقق منه من ملخص الخاضع للضريبة)
-• إقرار بالمؤسسات الفردية المملوكة إذا كان الكيان مؤسسة فردية (تحقق من المالك عبر رقم الهوية)</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Whichever is earlier: the turnover date or the MOA date</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Whichever is earlier: the turnover date or the MOA date</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>الأسبق بين تاريخ حجم الأعمال وتاريخ عقد التأسيس</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>lc-03, lc-05, cm-01, cm-02</t>
         </is>
@@ -6219,38 +6632,20 @@
           <t>Business no longer making taxable supplies</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>النشاط لم يعد يقدم توريدات خاضعة للضريبة</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>• MOA or contract evidencing the change in legal status
 • Previous and current trade licence
 • Financial declaration from registration date until today (can be checked from Taxpayer Overview)</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>• عقد التأسيس أو العقد المثبت لتغيير الشكل القانوني
-• الرخصة التجارية السابقة والحالية
-• بيان مالي من تاريخ التسجيل حتى اليوم (يمكن التحقق منه من ملخص الخاضع للضريبة)</t>
-        </is>
-      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Whichever is earlier: the turnover date or the MOA date</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Whichever is earlier: the turnover date or the MOA date</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>الأسبق بين تاريخ حجم الأعمال وتاريخ عقد التأسيس</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>lc-03, lc-05, cm-01</t>
         </is>
@@ -6280,38 +6675,20 @@
           <t>Business no longer making taxable supplies</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>النشاط لم يعد يقدم توريدات خاضعة للضريبة</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>• Amended MOA or any document evidencing the change
 • Previous and current trade licence
 • Financial declaration from registration date until today (can be checked from Taxpayer Overview)</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>• عقد التأسيس المعدّل أو أي مستند يثبت التغيير
-• الرخصة التجارية السابقة والحالية
-• بيان مالي من تاريخ التسجيل حتى اليوم (يمكن التحقق منه من ملخص الخاضع للضريبة)</t>
-        </is>
-      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Whichever is earlier: the turnover date or the amended MOA date</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Whichever is earlier: the turnover date or the amended MOA date</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>الأسبق بين تاريخ حجم الأعمال وتاريخ عقد التأسيس المعدّل</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>lc-04, lc-05, cm-01</t>
         </is>
@@ -6337,46 +6714,26 @@
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>• MOA or contract evidencing the change in legal status
 • Previous and current trade licence
 • Financial declaration from registration date until today (can be checked from Taxpayer Overview)</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>• عقد التأسيس أو العقد المثبت لتغيير الشكل القانوني
-• الرخصة التجارية السابقة والحالية
-• بيان مالي من تاريخ التسجيل حتى اليوم (يمكن التحقق منه من ملخص الخاضع للضريبة)</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Based on turnover, if accepted</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>بحسب حجم الأعمال في حال القبول</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>• Turnover above the voluntary threshold → reject and ask to apply for a VAT amendment
 • Turnover below the voluntary threshold → accept, with basis “below voluntary threshold”
 • To reject, use the rejection comment “change does not meet the conditions”</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>• حجم الأعمال أعلى من الحد الاختياري ← رفض الطلب وطلب التقدم بتعديل التسجيل
-• حجم الأعمال أقل من الحد الاختياري ← قبول الطلب على أساس «أقل من الحد الاختياري»
-• للرفض استخدم تعليق الرفض «التغيير لا يستوفي الشروط»</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>lc-03, lc-05, cm-01</t>
         </is>
@@ -6402,44 +6759,25 @@
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>• Amended MOA
 • Previous and current trade licence
 • Financial declaration from registration date until today (can be checked from Taxpayer Overview)</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>• عقد التأسيس المعدّل
-• الرخصة التجارية السابقة والحالية
-• بيان مالي من تاريخ التسجيل حتى اليوم (يمكن التحقق منه من ملخص الخاضع للضريبة)</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Based on turnover, if accepted</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>بحسب حجم الأعمال في حال القبول</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>• Turnover above the voluntary threshold → reject and ask to apply for a VAT amendment
 • Turnover below the voluntary threshold → accept, with basis “below voluntary threshold”</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>• حجم الأعمال أعلى من الحد الاختياري ← رفض الطلب وطلب التقدم بتعديل التسجيل
-• حجم الأعمال أقل من الحد الاختياري ← قبول الطلب على أساس «أقل من الحد الاختياري»</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>lc-04, lc-05, cm-01</t>
         </is>
@@ -6469,12 +6807,7 @@
           <t>Business no longer making taxable supplies</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>النشاط لم يعد يقدم توريدات خاضعة للضريبة</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>• Sale contract
 • Previous and current trade licence
@@ -6482,27 +6815,13 @@
 • Declaration of sole establishments owned, if the entity is a sole establishment (check the owner from the ID number)</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>• عقد البيع
-• الرخصة التجارية السابقة والحالية
-• بيان مالي من تاريخ التسجيل حتى اليوم (يمكن التحقق منه من ملخص الخاضع للضريبة)
-• إقرار بالمؤسسات الفردية المملوكة إذا كان الكيان مؤسسة فردية (تحقق من المالك عبر رقم الهوية)</t>
-        </is>
-      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Whichever is earlier: the turnover date or the sale contract date</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Whichever is earlier: the turnover date or the sale contract date</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>الأسبق بين تاريخ حجم الأعمال وتاريخ عقد البيع</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>lc-07, lc-05, cm-01, cm-02</t>
         </is>
@@ -6532,44 +6851,23 @@
           <t>Business no longer making taxable supplies</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>النشاط لم يعد يقدم توريدات خاضعة للضريبة</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>• Cancellation certificate, MOA/contract, or sale contract (as applicable)
 • Declaration of sole establishments owned, if the entity is a sole establishment (check the owner from the ID number)</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>• شهادة الإلغاء أو عقد التأسيس/العقد أو عقد البيع (بحسب الحالة)
-• إقرار بالمؤسسات الفردية المملوكة إذا كان الكيان مؤسسة فردية (تحقق من المالك عبر رقم الهوية)</t>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20 days after the effective registration date</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>• Compare the registration application date with the date of the change in the trade licence</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20 days after the effective registration date</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>20 يوماً بعد تاريخ سريان التسجيل</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>• Compare the registration application date with the date of the change in the trade licence</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>• قارن بين تاريخ طلب التسجيل وتاريخ التغيير في الرخصة التجارية</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>lc-01, lc-03, lc-07, cm-02</t>
         </is>
@@ -6599,38 +6897,20 @@
           <t>Making taxable supplies, but below the voluntary threshold</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>توريدات خاضعة للضريبة أقل من الحد الاختياري</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>• Declaration letter that the entity will not reach the mandatory threshold next month
 • Financial declaration from registration date until today (can be checked from Taxpayer Overview)
 • Declaration of sole establishments owned, if the entity is a sole establishment (check the owner from the ID number)</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>• خطاب إقرار بأن الكيان لن يتجاوز الحد الإلزامي خلال الشهر القادم
-• بيان مالي من تاريخ التسجيل حتى اليوم (يمكن التحقق منه من ملخص الخاضع للضريبة)
-• إقرار بالمؤسسات الفردية المملوكة إذا كان الكيان مؤسسة فردية (تحقق من المالك عبر رقم الهوية)</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>The date the taxable supplies fell below the threshold</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>The date the taxable supplies fell below the threshold</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>تاريخ انخفاض التوريدات الخاضعة للضريبة دون الحد</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>cm-03, cm-01, cm-02</t>
         </is>
@@ -6660,38 +6940,20 @@
           <t>Making taxable supplies, below the mandatory but above the voluntary threshold</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>توريدات خاضعة للضريبة أقل من الحد الإلزامي وأعلى من الاختياري</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>• Declaration letter that the entity will not reach the mandatory threshold next month
 • Financial declaration from registration date until today (can be checked from Taxpayer Overview)
 • Declaration of sole establishments owned, if the entity is a sole establishment (check the owner from the ID number)</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>• خطاب إقرار بأن الكيان لن يتجاوز الحد الإلزامي خلال الشهر القادم
-• بيان مالي من تاريخ التسجيل حتى اليوم (يمكن التحقق منه من ملخص الخاضع للضريبة)
-• إقرار بالمؤسسات الفردية المملوكة إذا كان الكيان مؤسسة فردية (تحقق من المالك عبر رقم الهوية)</t>
-        </is>
-      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Based on turnover</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Based on turnover</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>بحسب حجم الأعمال</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>cm-03, cm-01, cm-02</t>
         </is>
@@ -6721,44 +6983,23 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>أخرى</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>• TRN of the main company (compare both trade licences: same owner and legal status)
 • Declaration of filing under the main company</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>• رقم التسجيل الضريبي للشركة الرئيسية (قارن الرخصتين: المالك والشكل القانوني نفسه)
-• إقرار بتقديم الإقرارات مع الشركة الرئيسية</t>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>As per the review date</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>• Confirm the taxpayer will continue filing under the TRN whose turnover is above the threshold</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>As per the review date</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>بحسب تاريخ المراجعة</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>• Confirm the taxpayer will continue filing under the TRN whose turnover is above the threshold</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>• تأكد من أن الخاضع للضريبة سيستمر في تقديم الإقرارات برقم التسجيل الذي يتجاوز حجم أعماله الحد</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>mt-01, mt-02</t>
         </is>
@@ -6788,36 +7029,19 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>أخرى</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>• TRN of the main company (check the owner of the LLC licence)
 • Declaration of filing under the main company</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>• رقم التسجيل الضريبي للشركة الرئيسية (تحقق من مالك رخصة الشركة)
-• إقرار بتقديم الإقرارات مع الشركة الرئيسية</t>
-        </is>
-      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>As per the review date</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>As per the review date</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>بحسب تاريخ المراجعة</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>mt-01, mt-02</t>
         </is>
@@ -6847,44 +7071,23 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>أخرى</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>• TRN of the other entity (compare both licences: same owner and legal status)
 • Declaration of filing under the main company</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>• رقم التسجيل الضريبي للكيان الآخر (قارن الرخصتين: المالك والشكل القانوني نفسه)
-• إقرار بتقديم الإقرارات مع الشركة الرئيسية</t>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>As per the review date</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>• Confirm continued filing under the TRN with turnover above the threshold, and that it covers both VAT and Corporate Tax where required</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>As per the review date</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>بحسب تاريخ المراجعة</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>• Confirm continued filing under the TRN with turnover above the threshold, and that it covers both VAT and Corporate Tax where required</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>• تأكد من استمرار تقديم الإقرارات برقم التسجيل الذي يتجاوز حجم أعماله الحد، وأنه يشمل ضريبة القيمة المضافة وضريبة الشركات عند الاقتضاء</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>mt-03, mt-02</t>
         </is>
@@ -6910,40 +7113,23 @@
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>• Financial declaration from registration date until today (can be checked from Taxpayer Overview)</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>• Financial declaration from registration date until today (can be checked from Taxpayer Overview)</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>• بيان مالي من تاريخ التسجيل حتى اليوم (يمكن التحقق منه من ملخص الخاضع للضريبة)</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
           <t>If all licences were cancelled, sold or changed: whichever is earlier, the turnover or the last change</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>إذا أُلغيت جميع الرخص أو بيعت أو تغيّرت: الأسبق بين حجم الأعمال وآخر تغيير</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>• Turnover above the voluntary threshold → reject and ask to apply for a VAT amendment
 • Turnover below the voluntary threshold → accept, with basis “below voluntary threshold”</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>• حجم الأعمال أعلى من الحد الاختياري ← رفض الطلب وطلب التقدم بتعديل التسجيل
-• حجم الأعمال أقل من الحد الاختياري ← قبول الطلب على أساس «أقل من الحد الاختياري»</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>cm-01, lc-01, lc-07</t>
         </is>
@@ -6973,46 +7159,24 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>أخرى</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>• TRN of the main company (compare both licences: same owner and legal status)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>• TRN of the main company (compare both licences: same owner and legal status)</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>• رقم التسجيل الضريبي للشركة الرئيسية (قارن الرخصتين)</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
           <t>As per the review date</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>بحسب تاريخ المراجعة</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>• All branches are treated the same, even if the entity was a tax group member
 • A branch of a foreign company is treated as a normal trade licence and reviewed as a normal application
 • A branch owned by a different owner is reviewed as a normal application</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>• تُعامل جميع الفروع بالطريقة نفسها حتى لو كان الكيان عضواً في مجموعة ضريبية
-• فرع الشركة الأجنبية يُعامل كرخصة عادية ويُراجع كطلب عادي
-• الفرع المملوك لمالك مختلف يُراجع كطلب عادي</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>mt-04, mt-05</t>
         </is>
@@ -7042,34 +7206,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>أخرى</t>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>• Declaration of applying for a registration exception once approved</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>• Declaration of applying for a registration exception once approved</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>• إقرار بالتقدم بطلب الاستثناء من التسجيل بعد الموافقة</t>
-        </is>
-      </c>
+          <t>As per the review date</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>As per the review date</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>بحسب تاريخ المراجعة</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>sp-01</t>
         </is>
@@ -7099,36 +7247,19 @@
           <t>Making taxable supplies, but below the voluntary threshold</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>توريدات خاضعة للضريبة أقل من الحد الاختياري</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>• Declaration letter that the entity will not reach the mandatory threshold next month
 • Declaration of applying for a registration exception once approved</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>• خطاب إقرار بأن الكيان لن يتجاوز الحد الإلزامي خلال الشهر القادم
-• إقرار بالتقدم بطلب الاستثناء من التسجيل بعد الموافقة</t>
-        </is>
-      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Based on turnover</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Based on turnover</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>بحسب حجم الأعمال</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>cm-03, sp-01</t>
         </is>
@@ -7158,46 +7289,24 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>أخرى</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>• If a registration reference number for a new TRN was provided: check its status and contact the Registration team
 • Declaration letter that the entity will not reach the mandatory threshold next month</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>• إذا قُدّم رقم مرجعي لطلب تسجيل جديد: تحقق من حالته وتواصل مع فريق التسجيل
-• خطاب إقرار بأن الكيان لن يتجاوز الحد الإلزامي خلال الشهر القادم</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>As per the review date (or turnover if accepted as below threshold)</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>بحسب تاريخ المراجعة (أو حجم الأعمال إذا قُبل كأقل من الحد)</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>• First confirm from Taxpayer Overview that the entity type really does not match the licence
 • If taxable supplies are below the voluntary threshold, accept with basis “below voluntary threshold” instead of rejecting</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>• تأكد أولاً من ملخص الخاضع للضريبة أن نوع الكيان لا يطابق الرخصة فعلاً
-• إذا كانت التوريدات أقل من الحد الاختياري، اقبل الطلب على أساس «أقل من الحد الاختياري» بدلاً من الرفض</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>lc-08</t>
         </is>
@@ -7223,44 +7332,25 @@
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>• Financial declaration from registration date until today (can be checked from Taxpayer Overview)
 • Letter from the entity confirming it stopped making taxable supplies</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>• بيان مالي من تاريخ التسجيل حتى اليوم (يمكن التحقق منه من ملخص الخاضع للضريبة)
-• خطاب من الكيان يؤكد التوقف عن التوريدات الخاضعة للضريبة</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Based on turnover</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>بحسب حجم الأعمال</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>• Less than one year since registration (or sales in each of the last 12 months) → basis: Other
 • One year or more since registration, or no sales in the last 12 months → basis: no longer making taxable supplies
 • Foreign companies without a trade licence and online businesses must register from the first dirham of sales</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>• أقل من سنة منذ التسجيل (أو مبيعات في كل شهر من آخر 12 شهراً) ← الأساس: أخرى
-• سنة أو أكثر منذ التسجيل أو لا مبيعات في آخر 12 شهراً ← الأساس: لم يعد يقدم توريدات خاضعة
-• الشركات الأجنبية بلا رخصة تجارية والأنشطة الإلكترونية ملزمة بالتسجيل من أول درهم مبيعات</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>cm-01, sp-02</t>
         </is>
@@ -7286,42 +7376,24 @@
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>• Financial declaration from registration date until today (can be checked from Taxpayer Overview)
 • Letter from the entity confirming it stopped making taxable supplies</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>• بيان مالي من تاريخ التسجيل حتى اليوم (يمكن التحقق منه من ملخص الخاضع للضريبة)
-• خطاب من الكيان يؤكد التوقف عن التوريدات الخاضعة للضريبة</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Based on turnover</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>بحسب حجم الأعمال</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>• Same one-year rule as online businesses for choosing the basis
 • A foreign company with a UAE trade licence is reviewed as a normal application</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>• تطبق قاعدة السنة نفسها المطبقة على الأنشطة الإلكترونية لاختيار الأساس
-• الشركة الأجنبية التي تحمل رخصة تجارية في الدولة تُراجع كطلب عادي</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>cm-01, sp-02</t>
         </is>
@@ -7351,44 +7423,23 @@
           <t>Business no longer making taxable supplies</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>النشاط لم يعد يقدم توريدات خاضعة للضريبة</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>• Last invoice received as a board member
 • Declaration of sole establishments owned, if the entity is a sole establishment (check the owner from the ID number)</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>• آخر فاتورة مستلمة بصفة عضو مجلس إدارة
-• إقرار بالمؤسسات الفردية المملوكة إذا كان الكيان مؤسسة فردية (تحقق من المالك عبر رقم الهوية)</t>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Per the last invoice; if the invoice is dated after 01/01/2023 but relates to a period after that date, the eligible date is 01/01/2023</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>• If the invoice relates to a period before 01/01/2023, make sure the amount was declared in the return</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Per the last invoice; if the invoice is dated after 01/01/2023 but relates to a period after that date, the eligible date is 01/01/2023</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>بحسب آخر فاتورة؛ وإذا كانت الفاتورة بعد 01/01/2023 وتخص فترة بعد ذلك التاريخ فتاريخ الأهلية هو 01/01/2023</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>• If the invoice relates to a period before 01/01/2023, make sure the amount was declared in the return</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>• إذا كانت الفاتورة تخص فترة قبل 01/01/2023، تأكد من الإفصاح عن المبلغ في الإقرار</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>se-01, se-02, cm-02</t>
         </is>
@@ -7418,34 +7469,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>أخرى</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>As per the review date</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>• Director functions performed by a natural person are not a supply of services from 01/01/2023</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>As per the review date</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>بحسب تاريخ المراجعة</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>• Director functions performed by a natural person are not a supply of services from 01/01/2023</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>• مهام عضو مجلس الإدارة التي يؤديها شخص طبيعي ليست توريداً للخدمات اعتباراً من 01/01/2023</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>se-02, cm-06</t>
         </is>
@@ -7471,40 +7506,23 @@
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>• Clarification of the reason for deregistration</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>• Clarification of the reason for deregistration</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>• توضيح سبب إلغاء التسجيل</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
           <t>Registered before 15/11/2024 → 15/11/2024; registered after → as per the review date</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>مسجل قبل 15/11/2024 ← 15/11/2024؛ مسجل بعده ← بحسب تاريخ المراجعة</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>• Trade licence issued by a UAE authority → proceed (basis: no longer making taxable supplies, or Other if registered after 15/11/2024)
 • No UAE trade licence → reject; supplies of funds are taxable supplies</t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>• الرخصة صادرة من جهة في الدولة ← المتابعة (الأساس: لم يعد يقدم توريدات خاضعة، أو أخرى إذا سُجل بعد 15/11/2024)
-• لا توجد رخصة في الدولة ← رفض؛ توريدات الصناديق خاضعة للضريبة</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>se-03, cm-06</t>
         </is>
@@ -7534,34 +7552,18 @@
           <t>Business no longer making taxable supplies</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>النشاط لم يعد يقدم توريدات خاضعة للضريبة</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>04/12/2019</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>• Rights and obligations transferred to Management Entities on 03/11/2019; deregistration was due within 20 business days</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>04/12/2019</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>04/12/2019</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>• Rights and obligations transferred to Management Entities on 03/11/2019; deregistration was due within 20 business days</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>• انتقلت الحقوق والالتزامات إلى جهات الإدارة في 03/11/2019 وكان إلغاء التسجيل مستحقاً خلال 20 يوم عمل</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>se-12</t>
         </is>
@@ -7591,26 +7593,14 @@
           <t>Business no longer making taxable supplies</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>النشاط لم يعد يقدم توريدات خاضعة للضريبة</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Based on the last taxable invoice</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Based on the last taxable invoice</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>بحسب آخر فاتورة ضريبية</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>lc-09, cm-01</t>
         </is>
@@ -7636,8 +7626,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>• Completion certificate
 • Sale contract if sold
@@ -7645,39 +7634,19 @@
 • Declaration of sole establishments owned, if the entity is a sole establishment (check the owner from the ID number)</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>• شهادة الإنجاز
-• عقد البيع في حال البيع
-• بيان مالي من تاريخ التسجيل حتى اليوم (يمكن التحقق منه من ملخص الخاضع للضريبة)
-• إقرار بالمؤسسات الفردية المملوكة إذا كان الكيان مؤسسة فردية (تحقق من المالك عبر رقم الهوية)</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Completion certificate older than 3 years → the day after the 3 years; sale → sale contract date</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>شهادة الإنجاز أقدم من 3 سنوات ← اليوم التالي لانقضاء 3 سنوات؛ البيع ← تاريخ عقد البيع</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>• Completion certificate not older than 3 years → basis: Other
 • Completion certificate older than 3 years → basis: no longer making taxable supplies
 • Property for personal use → wrong registration, basis: Other</t>
         </is>
       </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>• شهادة الإنجاز لا تتجاوز 3 سنوات ← الأساس: أخرى
-• شهادة الإنجاز تتجاوز 3 سنوات ← الأساس: لم يعد يقدم توريدات خاضعة
-• عقار للاستخدام الشخصي ← تسجيل خاطئ، الأساس: أخرى</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>se-08, se-09, cm-01, cm-02</t>
         </is>
@@ -7703,44 +7672,25 @@
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>• Completion certificate
 • Sale contract if sold
 • Financial declaration from registration date until today (can be checked from Taxpayer Overview)</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>• شهادة الإنجاز
-• عقد البيع في حال البيع
-• بيان مالي من تاريخ التسجيل حتى اليوم (يمكن التحقق منه من ملخص الخاضع للضريبة)</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Based on turnover, or the sale contract date if sold</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>بحسب حجم الأعمال، أو تاريخ عقد البيع في حال البيع</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>• Stop counting zero-rated supplies after 3 years from the completion certificate; count only the commercial part (5% sales)
 • Below voluntary / below mandatory → the corresponding threshold basis; sale → no longer making taxable supplies</t>
         </is>
       </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>• توقف عن احتساب التوريدات بنسبة الصفر بعد 3 سنوات من شهادة الإنجاز واحتسب الجزء التجاري فقط (مبيعات 5%)
-• أقل من الاختياري / أقل من الإلزامي ← أساس الحد المقابل؛ البيع ← لم يعد يقدم توريدات خاضعة</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>se-08, se-09, cm-01, cm-03</t>
         </is>
@@ -7766,42 +7716,24 @@
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>• Sale contracts of all properties sold
 • Financial declaration from registration date until today (can be checked from Taxpayer Overview)</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>• عقود بيع جميع العقارات المباعة
-• بيان مالي من تاريخ التسجيل حتى اليوم (يمكن التحقق منه من ملخص الخاضع للضريبة)</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Multiple properties sold: whichever is earlier, turnover or the last sale contract</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>عدة عقارات مباعة: الأسبق بين حجم الأعمال وآخر عقد بيع</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>• Registered only to pay 5% on the sale of a single (or several) commercial property with no continuing business → wrong registration, basis: Other
 • Multiple properties, continuing then stopped → no longer making taxable supplies; still supplying below threshold → threshold basis</t>
         </is>
       </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>• سجل فقط لسداد 5% على بيع عقار تجاري واحد (أو أكثر) دون نشاط مستمر ← تسجيل خاطئ، الأساس: أخرى
-• عدة عقارات ثم توقف ← لم يعد يقدم توريدات خاضعة؛ ما زال يورد دون الحد ← أساس الحد</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>se-09, se-10, cm-01</t>
         </is>
@@ -7831,38 +7763,20 @@
           <t>Business no longer making taxable supplies</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>النشاط لم يعد يقدم توريدات خاضعة للضريبة</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>• Certificate of succession
 • Financial declaration from registration date until today (can be checked from Taxpayer Overview)
 • Declaration of sole establishments owned, if the entity is a sole establishment (check the owner from the ID number)</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>• إعلام الوراثة
-• بيان مالي من تاريخ التسجيل حتى اليوم (يمكن التحقق منه من ملخص الخاضع للضريبة)
-• إقرار بالمؤسسات الفردية المملوكة إذا كان الكيان مؤسسة فردية (تحقق من المالك عبر رقم الهوية)</t>
-        </is>
-      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Whichever is earlier: the turnover date or the succession certificate date</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Whichever is earlier: the turnover date or the succession certificate date</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>الأسبق بين تاريخ حجم الأعمال وتاريخ إعلام الوراثة</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>se-04, cm-01, cm-02</t>
         </is>
@@ -7892,42 +7806,22 @@
           <t>Business no longer making taxable supplies</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>النشاط لم يعد يقدم توريدات خاضعة للضريبة</t>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>• Cabinet Decision removing the entity from the Government Entities list</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>• Cabinet Decision removing the entity from the Government Entities list</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>• قرار مجلس الوزراء بشطب الجهة من قائمة الجهات الحكومية</t>
+          <t>Cabinet Decision date; if issued while in a tax group → TRN activation date</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>• Turnover is not considered for this case</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Cabinet Decision date; if issued while in a tax group → TRN activation date</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>تاريخ قرار مجلس الوزراء؛ وإذا صدر أثناء عضوية مجموعة ضريبية ← تاريخ تفعيل رقم التسجيل</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>• Turnover is not considered for this case</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>• لا يُؤخذ حجم الأعمال في الاعتبار في هذه الحالة</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>se-05</t>
         </is>
@@ -7957,42 +7851,22 @@
           <t>Business no longer making taxable supplies</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>النشاط لم يعد يقدم توريدات خاضعة للضريبة</t>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>• Cabinet Decision removing the entity from the Charities list</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>• Cabinet Decision removing the entity from the Charities list</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>• قرار مجلس الوزراء بشطب الجهة من قائمة الجهات الخيرية</t>
+          <t>Cabinet Decision date; if issued while in a tax group → TRN activation date</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>• Turnover is not considered for this case</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Cabinet Decision date; if issued while in a tax group → TRN activation date</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>تاريخ قرار مجلس الوزراء؛ وإذا صدر أثناء عضوية مجموعة ضريبية ← تاريخ تفعيل رقم التسجيل</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>• Turnover is not considered for this case</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>• لا يُؤخذ حجم الأعمال في الاعتبار في هذه الحالة</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>se-06</t>
         </is>
@@ -8022,36 +7896,19 @@
           <t>Business no longer making taxable supplies</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>النشاط لم يعد يقدم توريدات خاضعة للضريبة</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>• Last contract with Global Village
 • Financial declaration (more than one season)</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>• آخر عقد مع القرية العالمية
-• بيان مالي (أكثر من موسم)</t>
-        </is>
-      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>One season → last day of the signed contract; more than one season → based on turnover</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>One season → last day of the signed contract; more than one season → based on turnover</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>موسم واحد ← آخر يوم في العقد الموقع؛ أكثر من موسم ← بحسب حجم الأعمال</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="3" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>se-07, cm-01</t>
         </is>
@@ -8081,26 +7938,14 @@
           <t>Business no longer making taxable supplies</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>النشاط لم يعد يقدم توريدات خاضعة للضريبة</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2022 (last day of EXPO 2020)</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2022 (last day of EXPO 2020)</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>31/03/2022 (آخر يوم في إكسبو 2020)</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>cm-01</t>
         </is>
@@ -8126,28 +7971,17 @@
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>• Documents of the underlying case (cancellation, change of legal status, sale, threshold, branch)</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>• Documents of the underlying case (cancellation, change of legal status, sale, threshold, branch)</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>• مستندات الحالة الأساسية (إلغاء، تغيير شكل قانوني، بيع، حد التسجيل، فرع)</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
           <t>Never before the TRN activation date shown in the tax group application status log</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>لا يسبق أبداً تاريخ تفعيل رقم التسجيل المبين في سجل حالة طلب المجموعة الضريبية</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>• Open the group deregistration/amendment application and read the processed date from the status log: that is the TRN activation date
 • If the cancellation, change or sale happened while the entity was in the tax group → eligible date is the TRN activation date
@@ -8156,16 +7990,7 @@
 • Branch with a UAE main licence → as per the review date; branch of a foreign company → reviewed like case 1</t>
         </is>
       </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>• افتح طلب إلغاء/تعديل المجموعة واقرأ تاريخ المعالجة من سجل الحالة: هذا هو تاريخ تفعيل رقم التسجيل
-• إذا حدث الإلغاء أو التغيير أو البيع أثناء عضوية الكيان في المجموعة الضريبية ← تاريخ الأهلية هو تاريخ تفعيل رقم التسجيل
-• إذا حدث الإلغاء أو التغيير أو البيع بعد مغادرة المجموعة ← الأسبق بين حجم الأعمال وتاريخ الإلغاء أو التغيير أو البيع
-• أقل من الحد قبل الانضمام ← تاريخ الانخفاض؛ أثناء العضوية ← تاريخ تفعيل الرقم؛ بعد المغادرة ← تاريخ الانخفاض
-• فرع برخصة رئيسية داخل الدولة ← بحسب تاريخ المراجعة؛ فرع شركة أجنبية ← يُراجع كالحالة 1</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>se-11, cm-01, cm-02</t>
         </is>
@@ -8195,26 +8020,14 @@
           <t>External — documents to request</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>خارجي — مستندات تُطلب من الخاضع للضريبة</t>
-        </is>
-      </c>
+      <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>• Internal note to use after review: cessation / no revenue, revenue below 3M, or net profit below 375K</t>
         </is>
       </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>• الملاحظة الداخلية بعد المراجعة: توقف بلا إيرادات، أو إيرادات أقل من 3 ملايين، أو صافي ربح أقل من 375 ألفاً</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>ct-01, ct-02</t>
         </is>
@@ -8244,18 +8057,10 @@
           <t>External — documents to request</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>خارجي — مستندات تُطلب من الخاضع للضريبة</t>
-        </is>
-      </c>
+      <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="3" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="3" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="3" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>ct-04, ct-05, ct-06, ct-02</t>
         </is>
@@ -8285,18 +8090,10 @@
           <t>External — documents to request</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>خارجي — مستندات تُطلب من الخاضع للضريبة</t>
-        </is>
-      </c>
+      <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="3" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>ct-07, ct-03, ct-08</t>
         </is>
@@ -8326,26 +8123,14 @@
           <t>External — documents to request</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>خارجي — مستندات تُطلب من الخاضع للضريبة</t>
-        </is>
-      </c>
+      <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>• LLC → LLC sale without change of legal type → reject; the taxpayer must file an Amend Taxable Person Details application</t>
         </is>
       </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>• بيع ذ.م.م ← ذ.م.م دون تغيير الشكل القانوني ← رفض؛ يجب تقديم طلب تعديل بيانات الخاضع للضريبة</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>ct-09, ct-10, ct-02</t>
         </is>
@@ -8375,18 +8160,10 @@
           <t>External — documents to request</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>خارجي — مستندات تُطلب من الخاضع للضريبة</t>
-        </is>
-      </c>
+      <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="3" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>ct-11, ct-02</t>
         </is>
@@ -8416,18 +8193,10 @@
           <t>External — documents to request</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>خارجي — مستندات تُطلب من الخاضع للضريبة</t>
-        </is>
-      </c>
+      <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="3" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="3" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>ct-12, ct-13, ct-06, ct-02</t>
         </is>
@@ -8457,18 +8226,10 @@
           <t>External — documents to request</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>خارجي — مستندات تُطلب من الخاضع للضريبة</t>
-        </is>
-      </c>
+      <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>ct-09, ct-14, ct-15, ct-02</t>
         </is>
@@ -8498,26 +8259,14 @@
           <t>External — documents to request</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>خارجي — مستندات تُطلب من الخاضع للضريبة</t>
-        </is>
-      </c>
+      <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>• If the duplicate TRN is linked with VAT / Excise, that TRN must be deregistered — use the linked-TRN rejection</t>
         </is>
       </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>• إذا كان الرقم المكرر مرتبطاً بضريبة القيمة المضافة / الانتقائية، يجب إلغاء تسجيله — استخدم رفض الرقم المرتبط</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>ct-16</t>
         </is>
@@ -8547,18 +8296,10 @@
           <t>External — documents to request</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>خارجي — مستندات تُطلب من الخاضع للضريبة</t>
-        </is>
-      </c>
+      <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="3" t="inlineStr"/>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>ct-01, ct-19, ct-18, ct-02</t>
         </is>
@@ -8588,18 +8329,10 @@
           <t>External — documents to request</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>خارجي — مستندات تُطلب من الخاضع للضريبة</t>
-        </is>
-      </c>
+      <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="3" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr"/>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="3" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>ct-09, ct-17, ct-18, ct-15, ct-02</t>
         </is>
@@ -8629,18 +8362,10 @@
           <t>External — documents to request</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>خارجي — مستندات تُطلب من الخاضع للضريبة</t>
-        </is>
-      </c>
+      <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="3" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="3" t="inlineStr"/>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="3" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>ct-12, ct-13, ct-06</t>
         </is>
@@ -8670,18 +8395,10 @@
           <t>External — documents to request</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>خارجي — مستندات تُطلب من الخاضع للضريبة</t>
-        </is>
-      </c>
+      <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="3" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="3" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="3" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>ct-20, ct-18, ct-02</t>
         </is>
@@ -8711,26 +8428,14 @@
           <t>External — documents to request</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>خارجي — مستندات تُطلب من الخاضع للضريبة</t>
-        </is>
-      </c>
+      <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="3" t="inlineStr"/>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>• Revenue above AED 1 million in the calendar year → reject</t>
         </is>
       </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t>• إيرادات أعلى من مليون درهم في السنة الميلادية ← رفض</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>ct-18, ct-21</t>
         </is>
@@ -8760,28 +8465,15 @@
           <t>Internal</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>داخلي</t>
-        </is>
-      </c>
+      <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="3" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="3" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>• Eligibility: licence cancellation date = cessation date; tax amount AED 0; revenue &lt; 3M; net profit &lt; 375K; balance sheet clean
 • L2 uses the fast-track approval note</t>
         </is>
       </c>
-      <c r="L50" s="3" t="inlineStr">
-        <is>
-          <t>• الأهلية: تاريخ إلغاء الرخصة = تاريخ التوقف؛ مبلغ الضريبة صفر؛ الإيرادات أقل من 3 ملايين؛ صافي الربح أقل من 375 ألفاً؛ الميزانية سليمة
-• يستخدم المستوى الثاني ملاحظة اعتماد المسار السريع</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>ct-f1</t>
         </is>
